--- a/mevzuat listesi.xlsx
+++ b/mevzuat listesi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CREATOR\Dropbox\PC\Desktop\MEVZUAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80FEDAEB-AE7F-4D11-AE94-7F6C4970F441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A9E6C2-9E39-4665-9B7A-0F07A3A8CA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KANUN" sheetId="1" r:id="rId1"/>
@@ -24,12 +24,14 @@
     <sheet name="SÖZLEŞME VE PROTOKOL" sheetId="7" r:id="rId9"/>
     <sheet name="İÇ EMİR" sheetId="9" r:id="rId10"/>
     <sheet name="GENEL YAZI-TALİMAT" sheetId="8" r:id="rId11"/>
-    <sheet name="REHBER ve KLAVUZ" sheetId="10" r:id="rId12"/>
-    <sheet name="E-MAİL TALİMATLARI" sheetId="11" r:id="rId13"/>
-    <sheet name="DİĞER" sheetId="12" r:id="rId14"/>
+    <sheet name="REHBER ve KILAVUZ" sheetId="10" r:id="rId12"/>
+    <sheet name="DİĞER" sheetId="12" r:id="rId13"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">DİĞER!$A$1:$E$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">GENELGE!$A$1:$A$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">KANUN!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">YÖNETMELİK!$A$1:$E$157</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2345" uniqueCount="1012">
   <si>
     <t>numara</t>
   </si>
@@ -806,9 +808,6 @@
     <t>657/MD.DEĞİŞİK80</t>
   </si>
   <si>
-    <t>TURKUAZKART YÖNETMELİĞİ</t>
-  </si>
-  <si>
     <t>6735/MD.11, 25</t>
   </si>
   <si>
@@ -1436,9 +1435,6 @@
     <t>Maluliyet tespiti işlemleri</t>
   </si>
   <si>
-    <t>2018/8</t>
-  </si>
-  <si>
     <t>SGDP Yapılandırma</t>
   </si>
   <si>
@@ -1508,9 +1504,6 @@
     <t>Kreş ve gündüz bakımevleri işletme usul ve esasları</t>
   </si>
   <si>
-    <t>usul ve esaslar</t>
-  </si>
-  <si>
     <t>Sosyal Güvenlik Kurumu hukuk müşavirliği çalışma usul ve esasları</t>
   </si>
   <si>
@@ -1809,18 +1802,1329 @@
   </si>
   <si>
     <t>6331/MD.9</t>
+  </si>
+  <si>
+    <t>TÜRKİYE CUMHURİYETİ DEVLETİNİN PARA BİRİMİ HAKKINDA KANUN</t>
+  </si>
+  <si>
+    <t>arabulucu tutanaklarina istinaden hizmet verilmesi</t>
+  </si>
+  <si>
+    <t>aslı temin edilemeyen kanıtlayıcı belgeler</t>
+  </si>
+  <si>
+    <t>SGK HARCAMA BELGELERİ YÖNETMELİĞİ/MD.5</t>
+  </si>
+  <si>
+    <t>Aylık prim ve hizmet belgesi asma yükümlülüğü</t>
+  </si>
+  <si>
+    <t>5510/MD.86</t>
+  </si>
+  <si>
+    <t>BİLGİ GÜVENLİĞİ VE ŞİFRELERİN KORUNMASI</t>
+  </si>
+  <si>
+    <t>2010/66</t>
+  </si>
+  <si>
+    <t>Çalışılmadığına Dair Bildirime Bağlı İdari Para Cezalari</t>
+  </si>
+  <si>
+    <t>Devamlı Mahiyetteki İşyerlerinde Uzlaşma Uygulaması</t>
+  </si>
+  <si>
+    <t>5510/85</t>
+  </si>
+  <si>
+    <t>Fazla ve Yersiz Ödemelerin Takibi - Tahsili ve Terkini</t>
+  </si>
+  <si>
+    <t>Vekaletnamede Tereddüt Edilen Hususlar</t>
+  </si>
+  <si>
+    <t>Güvenlik Korucularının Sigortalılığı</t>
+  </si>
+  <si>
+    <t>Hakediş Ödemeleri ve Yapı Kullanma İzin Belgeleri</t>
+  </si>
+  <si>
+    <t>Hizmet Bildirme ve Birleştirme İşlemleri ve 4a Hizmet Borçlanma Programları</t>
+  </si>
+  <si>
+    <t>Hizmet Bildirme ve Birleştirme</t>
+  </si>
+  <si>
+    <t>İdari para cezalarında yapılacak indirim</t>
+  </si>
+  <si>
+    <t>İş Kazasına Uğrayan Sigortalılar İçin Düzenlenen Ek APHB'de Faydalanılan Asgari Ücret Desteği</t>
+  </si>
+  <si>
+    <t>İşveren Vekili</t>
+  </si>
+  <si>
+    <t>Kanunun ek 5 inci maddesi Kapsamında Sigortalılık</t>
+  </si>
+  <si>
+    <t>Kanunun ek 6 inci maddesi Kapsamında Sigortalılık</t>
+  </si>
+  <si>
+    <t>Mali Tatil Süresinde Çalışmadığına Dair Bildirim</t>
+  </si>
+  <si>
+    <t>Mobbing Şikayetleri</t>
+  </si>
+  <si>
+    <t>Muhtar Sigortalılar</t>
+  </si>
+  <si>
+    <t>Muhtar Sigortalıların Sigortalılıkları</t>
+  </si>
+  <si>
+    <t>Sanatçıların Sigortalılığı</t>
+  </si>
+  <si>
+    <t>Yabancı Dildeki Belgelerin Tercümesi</t>
+  </si>
+  <si>
+    <t>Yurtdışı işlemleri</t>
+  </si>
+  <si>
+    <t>ASGARİ İŞÇİLİK VE 102-E BENDİNİN UYGULANMASI</t>
+  </si>
+  <si>
+    <t>DİĞER</t>
+  </si>
+  <si>
+    <t>Çalıştay Raporu</t>
+  </si>
+  <si>
+    <t>4483 Sayılı Memurların ve Diğer Kamu Görevlilerinin Yargılanması Hakkında Kanun ve Uygulanması</t>
+  </si>
+  <si>
+    <t>EĞİTİM NOTU</t>
+  </si>
+  <si>
+    <t>Primlerde Uzlaşma</t>
+  </si>
+  <si>
+    <t>FATURA-HAKEDİŞ</t>
+  </si>
+  <si>
+    <t>Gemi Adamları</t>
+  </si>
+  <si>
+    <t>İHALELİ İŞLER VE ÖZEL BİNA İNŞAATI</t>
+  </si>
+  <si>
+    <t>İŞSİZLİK SİGORTASI</t>
+  </si>
+  <si>
+    <t>İç Denetim Birimi</t>
+  </si>
+  <si>
+    <t>2008/8</t>
+  </si>
+  <si>
+    <t>Organize sanayi ve endüstri bölgelerinde faaliyet gösteren işyerlerinin tek dosyada işlem görmesine izin verilmesi</t>
+  </si>
+  <si>
+    <t>5510 Sayılı Kanunun Kısa Vadeli Sigorta Kollarına İlişkin Uygulamaları</t>
+  </si>
+  <si>
+    <t>2008/16</t>
+  </si>
+  <si>
+    <t>2008/108</t>
+  </si>
+  <si>
+    <t>Hizmet Borçlanması İşlemleri</t>
+  </si>
+  <si>
+    <t>2008/111</t>
+  </si>
+  <si>
+    <t>2009/5</t>
+  </si>
+  <si>
+    <t>İsteğe bağlı sigortalılık işlemleri</t>
+  </si>
+  <si>
+    <t>Sigortalılık Sürelerinin Belirlenmesi</t>
+  </si>
+  <si>
+    <t>2009/17</t>
+  </si>
+  <si>
+    <t>Sigortalılık İşlemleri</t>
+  </si>
+  <si>
+    <t>2009/37</t>
+  </si>
+  <si>
+    <t>Fiili Hizmet Süresi Zammı Uygulaması</t>
+  </si>
+  <si>
+    <t>2009/79</t>
+  </si>
+  <si>
+    <t>İtibari Hizmet Süresi</t>
+  </si>
+  <si>
+    <t>2009/112</t>
+  </si>
+  <si>
+    <t>Basına Bilgi veya Demeç Verme</t>
+  </si>
+  <si>
+    <t>2010/2</t>
+  </si>
+  <si>
+    <t>Mal Bildirimi ve Kamu Görevlilleri Etik Sözleşmesi</t>
+  </si>
+  <si>
+    <t>2010/3</t>
+  </si>
+  <si>
+    <t>Resmi Yazışmalarda Uyulması Gereken Usul ve Esaslar</t>
+  </si>
+  <si>
+    <t>2010/14 SAYILI GENELGE</t>
+  </si>
+  <si>
+    <t>Güvenlik Kameraları</t>
+  </si>
+  <si>
+    <t>2010/26</t>
+  </si>
+  <si>
+    <t>Grup Başkanlıkları ve Görev Alanları</t>
+  </si>
+  <si>
+    <t>2010/36</t>
+  </si>
+  <si>
+    <t>KAMU HİZMETLERİNİN SUNUMUNDA UYULACAK USUL VE ESASLARA İLİŞKİN YÖNETMELİK</t>
+  </si>
+  <si>
+    <t>3056 SAYILI KHK/MD.2, 33</t>
+  </si>
+  <si>
+    <t>Vatandaşlarımıza Sunulan Hizmetlerin Sunumunda Uyulacak Hususlar</t>
+  </si>
+  <si>
+    <t>2010/54</t>
+  </si>
+  <si>
+    <t>Kendi Adına ve Hesabına Tarımsal Faaliyette Bulunan Sigortalılara İlişkin İşlemler</t>
+  </si>
+  <si>
+    <t>2010/77</t>
+  </si>
+  <si>
+    <t>Tahsis Uygulamaları</t>
+  </si>
+  <si>
+    <t>2010/99</t>
+  </si>
+  <si>
+    <t>Hizmet Borçlanma İşlemleri</t>
+  </si>
+  <si>
+    <t>2010/106</t>
+  </si>
+  <si>
+    <t>Silikozis hastaları ile ilgili iş ve işlemler</t>
+  </si>
+  <si>
+    <t>2011/27</t>
+  </si>
+  <si>
+    <t>Destek Hizmetleri İşlemleri</t>
+  </si>
+  <si>
+    <t>2011/28</t>
+  </si>
+  <si>
+    <t>2013/8</t>
+  </si>
+  <si>
+    <t>Harcama Yetkisi</t>
+  </si>
+  <si>
+    <t>2011/34</t>
+  </si>
+  <si>
+    <t>2011/35 SAYILI GENELGE</t>
+  </si>
+  <si>
+    <t>Yabancı uyrukluların sigortalılıkları</t>
+  </si>
+  <si>
+    <t>2011/43</t>
+  </si>
+  <si>
+    <t>Çalışma gücü ve meslekte kazanma gücü kaybı tespit işlemleri</t>
+  </si>
+  <si>
+    <t>2011/49</t>
+  </si>
+  <si>
+    <t>Kısa Vadeli Sigorta Kolları Uygulamaları</t>
+  </si>
+  <si>
+    <t>2011/50</t>
+  </si>
+  <si>
+    <t>2011/51</t>
+  </si>
+  <si>
+    <t>İş Kazası ve Meslek Hastalığı Vakalarının Çalışma Bölge Müdürlüklerine İntikal Ettirilmesi</t>
+  </si>
+  <si>
+    <t>2011/57</t>
+  </si>
+  <si>
+    <t>Kanuna Göre 4-1-(a) ve 4-1-(b) Kapsamındaki Sigortalıların Tahsis İşlemleri</t>
+  </si>
+  <si>
+    <t>2011/58</t>
+  </si>
+  <si>
+    <t>Fatura bedellerinin ödenmesi</t>
+  </si>
+  <si>
+    <t>2011/62</t>
+  </si>
+  <si>
+    <t>KAMU PERSONELİ GENEL TEBLİĞİ - SERİ NO: 6</t>
+  </si>
+  <si>
+    <t>KAMU PERSONELİ GENEL TEBLİĞİ - SERİ NO: 4</t>
+  </si>
+  <si>
+    <t>KAMU PERSONELİ GENEL TEBLİĞİ - SERİ NO: 3</t>
+  </si>
+  <si>
+    <t>KAMU PERSONELİ GENEL TEBLİĞİ - SERİ NO: 2</t>
+  </si>
+  <si>
+    <t>2011/66</t>
+  </si>
+  <si>
+    <t>Başarı, üstün başarı değerlendirmesi ve ödül işlemleri</t>
+  </si>
+  <si>
+    <t>Merkezi tahsilat sistemi</t>
+  </si>
+  <si>
+    <t>2011/71</t>
+  </si>
+  <si>
+    <t>Yeşil kart devri ve genel sağlık sigortası tescil işlemler</t>
+  </si>
+  <si>
+    <t>2012/2</t>
+  </si>
+  <si>
+    <t>2012/13</t>
+  </si>
+  <si>
+    <t>İş Kazası ve Meslek Hastalığı Bildirim Formunun Elektronik Ortamda Kuruma Gönderilmesi</t>
+  </si>
+  <si>
+    <t>Tamamlayıcı veya Destekleyici Sağlık Sigortası Uygulamaları</t>
+  </si>
+  <si>
+    <t>2012/25</t>
+  </si>
+  <si>
+    <t>2012/26 SAYILI GENELGE</t>
+  </si>
+  <si>
+    <t>Kurum alacaklarının terkini ve zamanaşımı</t>
+  </si>
+  <si>
+    <t>2012/27</t>
+  </si>
+  <si>
+    <t>2012/31</t>
+  </si>
+  <si>
+    <t>Sağlık Kurum ve Kuruluşlarınca Temin Edilen Tıbbi Malzeme Bedellerinin Ödenmesi</t>
+  </si>
+  <si>
+    <t>2012/33</t>
+  </si>
+  <si>
+    <t>Genel Sağlık Sigortası Bakımından Rücu ve Yersiz Ödemelerin Geri Alınması</t>
+  </si>
+  <si>
+    <t>2012/40</t>
+  </si>
+  <si>
+    <t>Sağlık Hizmet Sunucuları İnceleme ve Kontrol Standartları</t>
+  </si>
+  <si>
+    <t>2012/41 SAYILI GENELGE</t>
+  </si>
+  <si>
+    <t>Sosyal Güvenlik Denetmenleri Standartları</t>
+  </si>
+  <si>
+    <t>2013/5 SAYILI GENELGE</t>
+  </si>
+  <si>
+    <t>Çalışılmadığına Dair Bildirim Girişi</t>
+  </si>
+  <si>
+    <t>2013/19</t>
+  </si>
+  <si>
+    <t>SSİY/MD.40</t>
+  </si>
+  <si>
+    <t>2013/20</t>
+  </si>
+  <si>
+    <t>6385 sayılı Kanun Uygulamaları, Emzirme Ödeneği ile Diğer uygulamalar</t>
+  </si>
+  <si>
+    <t>2013/26</t>
+  </si>
+  <si>
+    <t>2013/31</t>
+  </si>
+  <si>
+    <t>İş Kazası ve Meslek Hastalıkları Soruşturulması</t>
+  </si>
+  <si>
+    <t>Kamu Denetçiliği Kurumuna Yapılan Şikayet Başvuruları</t>
+  </si>
+  <si>
+    <t>2013/36</t>
+  </si>
+  <si>
+    <t>UNVAN BAZINDA İŞ-GÖREV TANIMLARI KİTABI - 2012</t>
+  </si>
+  <si>
+    <t>UNVAN BAZINDA İŞ-GÖREV TANIMLARI KİTABI - 2014</t>
+  </si>
+  <si>
+    <t>2014/14 SAYILI GENELGE</t>
+  </si>
+  <si>
+    <t>iş kazaları</t>
+  </si>
+  <si>
+    <t>2014/16</t>
+  </si>
+  <si>
+    <t>saglik denetimi</t>
+  </si>
+  <si>
+    <t>2014/17</t>
+  </si>
+  <si>
+    <t>Aylık bağlandıktan sonra yurtdışında çalışanlar</t>
+  </si>
+  <si>
+    <t>2014/22</t>
+  </si>
+  <si>
+    <t>Anlaşmasız Sağlık Tesislerince Düzenlenen İstirhat Raporları İçin Onay Şartı Aranmaması Hakkında</t>
+  </si>
+  <si>
+    <t>2014/23</t>
+  </si>
+  <si>
+    <t>Mal Bildirimlerinin Yenilenmesi</t>
+  </si>
+  <si>
+    <t>2014/33</t>
+  </si>
+  <si>
+    <t>Çalışma Gücü Kaybı ile Meslekte Kazanma Gücü Kayıp Oranı Tespit İşlemleri</t>
+  </si>
+  <si>
+    <t>2015/27</t>
+  </si>
+  <si>
+    <t>Sağlık Hizmet Sunucularının İş Kazası Ve Meslek Hastalığı Bildirimi</t>
+  </si>
+  <si>
+    <t>Kısa vadeli sigorta kolları uygulamaları</t>
+  </si>
+  <si>
+    <t>2016/21</t>
+  </si>
+  <si>
+    <t>2016/23</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2886-4734 sayılı kanun kapsamı dışındaki özel seektörden özele verilen işlerde yapılacak işyeri tescili</t>
+  </si>
+  <si>
+    <t>2017/21</t>
+  </si>
+  <si>
+    <t>2016/11 sayılı genelge değişikliği</t>
+  </si>
+  <si>
+    <t>6824 Sayılı Kanun Gereği Yapılacak Genel Sağlık Sigortasına İlişkin İşlemler</t>
+  </si>
+  <si>
+    <t>2017/16</t>
+  </si>
+  <si>
+    <t>2015/25 Sayılı Genelgede Değişiklik</t>
+  </si>
+  <si>
+    <t>2017/19</t>
+  </si>
+  <si>
+    <t>KİMLİK BİLDİRME KANUNU</t>
+  </si>
+  <si>
+    <t>KİMLİK BİLDİRME KANUNUNUN UYGULANMASI İLE İLGİLİ YÖNETMELİK</t>
+  </si>
+  <si>
+    <t>UNVAN BAZINDA İŞ-GÖREV TANIMLARI KİTABI - 2017</t>
+  </si>
+  <si>
+    <t>2017/23 SAYILI GENELGE</t>
+  </si>
+  <si>
+    <t>Veri Sızıntısı Önleme-DLP</t>
+  </si>
+  <si>
+    <t>2017/28</t>
+  </si>
+  <si>
+    <t>SGK İPC UYGULAMASI KİTAPÇIĞI</t>
+  </si>
+  <si>
+    <t>KİTAPÇIK</t>
+  </si>
+  <si>
+    <t>2020/8 SAYILI GENELGE</t>
+  </si>
+  <si>
+    <t>4447 Sayılı Kanunun Geçici 17 nci Maddesinde Yer Alan İşveren Desteği</t>
+  </si>
+  <si>
+    <t>2017/10</t>
+  </si>
+  <si>
+    <t>Kurum Alacaklarının 7020 sayılı Kanun Uyarınca Yapılandırılması</t>
+  </si>
+  <si>
+    <t>2017/22</t>
+  </si>
+  <si>
+    <t>Kurum Rücuen Alacaklarının 7020 sayılı Kanun Uyarınca Yapılandırılması</t>
+  </si>
+  <si>
+    <t>SOSYAL GÜVENLİK KURUMU SİCİL AMİRLERİ YÖNETMELİĞİ</t>
+  </si>
+  <si>
+    <t>657/MD.112</t>
+  </si>
+  <si>
+    <t>SOSYAL GÜVENLİK KURUMU DİSİPLİN KOVUŞTURMALARI İLE DİSİPLİN CEZALARININ UYGULANMASINA VE TEBLİGAT İŞLEMLERİNE DAİR USUL VE ESASLAR</t>
+  </si>
+  <si>
+    <t>Disiplin Kurulları Ve Disiplin Amirleri Hakkında Yönetmelik</t>
+  </si>
+  <si>
+    <t>657/MD.DEĞİŞİK134</t>
+  </si>
+  <si>
+    <t>İNSAN KAYNAKLARI TERİMLERİ SÖZLÜĞÜ</t>
+  </si>
+  <si>
+    <t>SÖZLÜK</t>
+  </si>
+  <si>
+    <t>4 SAYILI CBK/MD.794</t>
+  </si>
+  <si>
+    <t>ASBEST SÖKÜMÜ İLE İLGİLİ EĞİTİM PROGRAMLARINA İLİŞKİN TEBLİĞ</t>
+  </si>
+  <si>
+    <t>ASBESTLE ÇALIŞMALARDA SAĞLIK VE GÜVENLİK ÖNLEMLERİ HAKKINDA YÖNETMELİK/MD.19, 20</t>
+  </si>
+  <si>
+    <t>BÜYÜK ENDÜSTRİYEL KAZALARIN ÖNLENMESİ VE ETKİLERİNİN AZALTILMASI HAKKINDA YÖNETMELİK</t>
+  </si>
+  <si>
+    <t>6331 - 2872 - 4 NOLU CBK</t>
+  </si>
+  <si>
+    <t>BÜYÜK ENDÜSTRİYEL KAZALARLA İLGİLİ HAZIRLANACAK BÜYÜK KAZA ÖNLEME POLİTİKA BELGESİ TEBLİĞİ</t>
+  </si>
+  <si>
+    <t>BÜYÜK ENDÜSTRİYEL KAZALARDA UYGULANACAK DÂHİLİ ACİL DURUM PLANLARI HAKKINDA TEBLİĞ</t>
+  </si>
+  <si>
+    <t>BÜYÜK ENDÜSTRİYEL KAZALARLA İLGİLİ HAZIRLANACAK BÜYÜK KAZA SENARYO DOKÜMANI TEBLİĞİ</t>
+  </si>
+  <si>
+    <t>BÜYÜK ENDÜSTRİYEL KAZALARLA İLGİLİ HAZIRLANACAK GÜVENLİK RAPORU TEBLİĞİ</t>
+  </si>
+  <si>
+    <t>İŞ SAĞLIĞI VE GÜVENLİĞİ İLE İLGİLİ ÇALIŞAN TEMSİLCİSİNİN NİTELİKLERİ VE SEÇİLME USUL VE ESASLARINA İLİŞKİN TEBLİĞ</t>
+  </si>
+  <si>
+    <t>6331 - 3146</t>
+  </si>
+  <si>
+    <t>ÇALIŞMA VE SOSYAL GÜVENLİK ALANINDA BAZI MALİ HÜKÜMLER HAKKINDA KANUN</t>
+  </si>
+  <si>
+    <t>ULUSAL İŞ SAĞLIĞI VE GÜVENLİĞİ KONSEYİ ÇALIŞMA USUL VE ESASLARI HAKKINDA YÖNETMELİK</t>
+  </si>
+  <si>
+    <t>6331 - 1 NOLU CBK</t>
+  </si>
+  <si>
+    <t>Titreşim Yönetmeliği</t>
+  </si>
+  <si>
+    <t>4857 SAYILI İŞ KANUNUNUN 65 İNCİ MADDESİNE GÖRE UYGULANACAK KISA ÇALIŞMA VE KISA ÇALIŞMA ÖDENEĞİNE İLİŞKİN TEBLİĞ (TEBLİĞ NO: 1)</t>
+  </si>
+  <si>
+    <t>4857/MD.65</t>
+  </si>
+  <si>
+    <t>GÜRÜLTÜ YÖNETMELİĞİ</t>
+  </si>
+  <si>
+    <t>4857/MD.78</t>
+  </si>
+  <si>
+    <t>KİŞİSEL KORUYUCU DONANIMLARLA İLGİLİ ONAYLANMIŞ KURULUŞLARIN GÖREVLENDİRİLMESİNE DAİR TEBLİĞ</t>
+  </si>
+  <si>
+    <t>ÜST KADEME KAMU YÖNETİCİLERİ İLE KAMU KURUM VE KURULUŞLARINDA ATAMA USÛLLERİNE DAİR CUMHURBAŞKANLIĞI KARARNAMESİ</t>
+  </si>
+  <si>
+    <t>TAHSİSTE VEKILIN AVUKAT, SM, SMMM OLMASINA GEREK OLMAMASI</t>
+  </si>
+  <si>
+    <t>2021/38</t>
+  </si>
+  <si>
+    <t>Sosyal Güvenlik Kurumunca Elektronik Ortamda Yapılacak Tebligat İşlemleri</t>
+  </si>
+  <si>
+    <t>5510 SAYILI KANUNUN 100 VE 102 NCI MADDELERİ KAPSAMINDAKİ KURUM UYGULAMALARI</t>
+  </si>
+  <si>
+    <t>Yabancı Memleketlerde Bulunanlara Tebliğ</t>
+  </si>
+  <si>
+    <t>Yurt Dısı Saglık Uygulamaları</t>
+  </si>
+  <si>
+    <t>BİLGİ YAZISI</t>
+  </si>
+  <si>
+    <t>KESİNLEŞMEYEN İŞ MAHKEMESİ KARARI - APHB VE İPC</t>
+  </si>
+  <si>
+    <t>YAPAY ZEKA SİSTEMLERİNİN KULLANIMINDA KAMU GÖREVLİLERİNİN UYMASI GEREKEN ETİK DAVRANIŞ İLKELERİ</t>
+  </si>
+  <si>
+    <t>Yabancı Uyruklu Çalısanların Sigortalılığı</t>
+  </si>
+  <si>
+    <t>YABANCI UYRUKLU KAÇAK İŞÇİLERİN PRİME ESAS KAZANCI</t>
+  </si>
+  <si>
+    <t>MÜTALAA</t>
+  </si>
+  <si>
+    <t>İZİNSİZ ÇALIŞTIĞI TESPİT EDİLEN YABANCILARIN DENETİM ELEMANLARINCA İVEDİLİKLE KOLLUK BİRİMLERİNE BİLDİRİLMESİ</t>
+  </si>
+  <si>
+    <t>SOSYAL GÜVENLİK KURUMUNCA ELEKTRONİK ORTAMDA OLUŞTURULAN ORTAK BİR VERİ TABANINDAN YARARLANMAK SURETİYLE YAPILACAK HARCAMALARDA VERİ GİRİŞİNİN GERÇEKLEŞTİRME İŞLEMİ/BELGESİ OLARAK KABUL EDİLMESİNE İLİŞKİN USUL VE ESASLAR</t>
+  </si>
+  <si>
+    <t>USUL VE ESASLAR</t>
+  </si>
+  <si>
+    <t>GEÇİCİ GÖREVLE ÜLKEMİZE GELEN YABANCI UYRUKLULARIN SİGORTALILIĞI HAKKINDA DUYURU</t>
+  </si>
+  <si>
+    <t>DUYURU</t>
+  </si>
+  <si>
+    <t>Toptan Ödemenin Ihyası Islemleri</t>
+  </si>
+  <si>
+    <t>2024/7</t>
+  </si>
+  <si>
+    <t>TASARRUF TEDBİRLERİ</t>
+  </si>
+  <si>
+    <t>SOSYAL GÜVENLİK KURUMU SÜPERVİZÖR USUL VE ESASLARI</t>
+  </si>
+  <si>
+    <t>4 NOLU CBK/MD.417</t>
+  </si>
+  <si>
+    <t>SOSYAL GÜVENLİK SÖZLEŞMESİ OLMAYAN ÜLKELERDE ÇALIŞTIRILAN TÜRK İŞÇİLER</t>
+  </si>
+  <si>
+    <t>SMS BİLGİLENDİRME SİSTEMİ</t>
+  </si>
+  <si>
+    <t>UZAKTAN BAĞLANTI YETKİSİ</t>
+  </si>
+  <si>
+    <t>SAVUNMA ALINMASI</t>
+  </si>
+  <si>
+    <t>SAĞLIK HİZMET SUNUCULARININ BASAMAKLANDIRILMASI</t>
+  </si>
+  <si>
+    <t>AYAKTA TEŞHİS VE TEDAVİ YAPILAN ÖZEL SAĞLIK KURULUŞLARI HAKKINDA YÖNETMELİK</t>
+  </si>
+  <si>
+    <t>1219 - 3359 - 3153 - 1 NOLU CBK</t>
+  </si>
+  <si>
+    <t>ÖZEL SAĞLIK KURUM VE KURULUŞLARININ İL SAĞLIK MÜDÜRLÜKLERİNCE DENETİMİNE İLİŞKİN USUL VE ESASLAR HAKKINDA YÖNERGE</t>
+  </si>
+  <si>
+    <t>SAĞLIK BAKANLIĞI</t>
+  </si>
+  <si>
+    <t>RESEN İŞYERİ TESCİLLERİ</t>
+  </si>
+  <si>
+    <t>Prime Esas Kazancın Üst Sınırını Aşan Primlerin İade İşlemleri</t>
+  </si>
+  <si>
+    <t>PASAPORT VE PASAPORT YERİNE GEÇEN BELGELER</t>
+  </si>
+  <si>
+    <t>BASINA BİLGİ VE DEMEÇ VERME</t>
+  </si>
+  <si>
+    <t>NOTER VEKİLLERİ</t>
+  </si>
+  <si>
+    <t>SOSYAL GÜVENLİK KURUMU NORM KADRO İLKE VE STANDARTLARINA DAİR USUL VE ESASLAR</t>
+  </si>
+  <si>
+    <t>5502/MD.24, 41</t>
+  </si>
+  <si>
+    <t>NAKİL DURUMUNDA ŞUBAT AYI BİLDİRİMİ</t>
+  </si>
+  <si>
+    <t>BAZI İŞ KOLLARINDA ASGARİ İŞÇİLİK ORANI TESPİTİ</t>
+  </si>
+  <si>
+    <t>SOSYAL GÜVENLİK KURUMU BAŞKANLIĞI MOBBINGIN (İŞ YERİNDE SİSTEMATİK PSİKOLOJİK TACİZ) ÖNLENMESİNE DAİR USUL ve ESASLAR</t>
+  </si>
+  <si>
+    <t>2011/2 BAŞBAKANLIK GENELGESİ</t>
+  </si>
+  <si>
+    <t>MESLEK HASTALIĞI TESPİT HASTANELERİ</t>
+  </si>
+  <si>
+    <t>Serbest Muhasebeci Mali Müşavirlerin Rapor Düzenleme Sınırı</t>
+  </si>
+  <si>
+    <t>MAL BİLDİRİMİNDE BULUNULMASI HAKKINDA YÖNETMELİK</t>
+  </si>
+  <si>
+    <t>3628 SAYILI MAL BİLDİRİMİNDE BULUNULMASI, RÜŞVET VE YOLSUZLUKLARLA MÜCADELE KANUNUNUN KOOPERATİFLERDE UYGULANMASINA DAİR TEBLİĞ</t>
+  </si>
+  <si>
+    <t>MADENLERDE İŞ KAZASI SONUCUNDA HAYATINI KAYBEDEN SİGORTALILARIN YAKINLARININ KAMUDA SÜREKLİ İŞÇİ KADROLARINA ATANMALARINA İLİŞKİN USUL VE ESASLAR</t>
+  </si>
+  <si>
+    <t>5510/MD.GEÇİCİ66</t>
+  </si>
+  <si>
+    <t>PERSONEL ÇALIŞTIRILMAKSIZIN SONUÇ KARŞILIĞI LABORATUVAR HİZMETLERİ</t>
+  </si>
+  <si>
+    <t>Kamu kurum ve kuruluslarının İş alanlarında çalıstırılan hükümlülerin sigortalılıkları hakkında</t>
+  </si>
+  <si>
+    <t>SGK İŞVEREN TEMSİLCİSİ UYGULAMA USUL VE ESASLARI</t>
+  </si>
+  <si>
+    <t>Kep ile Yapılan İş Kazası Bildirimleri</t>
+  </si>
+  <si>
+    <t>İŞ KAZASI TESPİTİNDE MESLEK KODU HAKKINDA DUYURU</t>
+  </si>
+  <si>
+    <t>5510 SAYILI KANUNUN 21 İNCİ MADDESİNİN 5 İNCİ FIKRASI HAKKINDA</t>
+  </si>
+  <si>
+    <t>TEFTİŞ DOSYALARININ HAZIRLANMASINDA UYULACAK ESASLAR</t>
+  </si>
+  <si>
+    <t>KISA VADELİ SİGORTA UYGULAMALARI</t>
+  </si>
+  <si>
+    <t>İdari Para Cezalarının İptali Için Açılan Davalarda Yapılacak Savunmalar</t>
+  </si>
+  <si>
+    <t>HASTANELERİN İŞ KAZASI BİLDİRİMLERİ - İPC HAKKINDA</t>
+  </si>
+  <si>
+    <t>Grup Başkanlıklarımızın Sorumluluk Alanları</t>
+  </si>
+  <si>
+    <t>Gemi Adamları G.S.S. Tescil Islemleri</t>
+  </si>
+  <si>
+    <t>GELİR VE AYLIK BİRLEŞMESİ</t>
+  </si>
+  <si>
+    <t>EMEKLİLİK HİZMETLERİ GENEL MÜDÜRLÜĞÜ</t>
+  </si>
+  <si>
+    <t>Genel Muhasebe Uygulamaları</t>
+  </si>
+  <si>
+    <t>Geçici Görevlendirmelerde Yemek Ücreti</t>
+  </si>
+  <si>
+    <t>E-REÇETE DUYURUSU</t>
+  </si>
+  <si>
+    <t>Emekli Ikramiyesi</t>
+  </si>
+  <si>
+    <t>Fiziki Tebligat Gönderme İşlemleri</t>
+  </si>
+  <si>
+    <t>Disiplin İş ve İşlemlerinde Dikkat Edilecek Hususlar</t>
+  </si>
+  <si>
+    <t>CUMHURBAŞKANLIĞI</t>
+  </si>
+  <si>
+    <t>SOSYAL GÜVENLİK KURUMU BİREYSEL ÖNERİ SİSTEMİ USUL VE ESASLARI</t>
+  </si>
+  <si>
+    <t>STRATEJİ GELİŞTİRME BİRİMLERİNİN ÇALIŞMA USUL VE ESASLARI HAKKINDA YÖNETMELİK</t>
+  </si>
+  <si>
+    <t>5018 - 5502</t>
+  </si>
+  <si>
+    <t>BELGENET EĞİTİMİ</t>
+  </si>
+  <si>
+    <t>ARAÇ BİLGİLERİNİN TALEP EDİLMESİ</t>
+  </si>
+  <si>
+    <t>APARTMAN VE SİTE YÖNETİMLERİNİN DEFTER TÜRLERİ HAKKINDA</t>
+  </si>
+  <si>
+    <t>7438 Sayılı Kanun ile 5510 Sayılı
+Kanuna Eklenen Geçici 95 inci Madde</t>
+  </si>
+  <si>
+    <t>2023/13</t>
+  </si>
+  <si>
+    <t>7417 Sayılı Kanunun Kurumumuz Görev Alanındaki Hükümlerinin Uygulanması</t>
+  </si>
+  <si>
+    <t>2023/1</t>
+  </si>
+  <si>
+    <t>Maluliyet ve ÇalıŞma Gücü Kaybı Tespit İşlemleri</t>
+  </si>
+  <si>
+    <t>2022/24</t>
+  </si>
+  <si>
+    <t>Avrupa Sosyal Güvenlik Sözlesmesi</t>
+  </si>
+  <si>
+    <t>2021/34</t>
+  </si>
+  <si>
+    <t>Sahte, Kontrollü Şüpheli İşyerleri İle İlgili Yapılacak İşlemler</t>
+  </si>
+  <si>
+    <t>2021/27</t>
+  </si>
+  <si>
+    <t>5510 SAYILI KANUNUN 4/1-b KAPSAMINDAKİ SİGORTALILIĞIN DURDURULMASI</t>
+  </si>
+  <si>
+    <t>2021/21</t>
+  </si>
+  <si>
+    <t>Sosyal Güvenlik Denetmenleri İş ve İşlemleri</t>
+  </si>
+  <si>
+    <t>2020/39</t>
+  </si>
+  <si>
+    <t>5434 TAHSİS</t>
+  </si>
+  <si>
+    <t>2020/22</t>
+  </si>
+  <si>
+    <t>2019/18</t>
+  </si>
+  <si>
+    <t>VAZİFE MALULLÜĞÜ</t>
+  </si>
+  <si>
+    <t>5510 SAYILI KANUNUN EK-9 UNCU MADDESİ KAPSAMINDA KONUT KAPICILIĞI İŞYERLERİNDE ÇALIŞANLAR</t>
+  </si>
+  <si>
+    <t>2019/6</t>
+  </si>
+  <si>
+    <t>2018/27</t>
+  </si>
+  <si>
+    <t>YURTDIŞI BORÇLANMA</t>
+  </si>
+  <si>
+    <t>2018/9</t>
+  </si>
+  <si>
+    <t>SSİY DEĞİŞİKLİKLERİ</t>
+  </si>
+  <si>
+    <t>2018/4</t>
+  </si>
+  <si>
+    <t>4-1-a ve 4-1-b Sigortalılarına İlişkin Tahsis Uygulamaları</t>
+  </si>
+  <si>
+    <t>Sosyal Güvenlik Kurumuna Ödenecek Başvuru, Aidat, İşlem ve Sözleşme Ücretlerine İlişkin Usul ve Esaslar</t>
+  </si>
+  <si>
+    <t>5510/MD.73</t>
+  </si>
+  <si>
+    <t>MUHTASAR VE PRİM HİZMET BEYANNAMESİ GENEL TEBLİĞİ</t>
+  </si>
+  <si>
+    <t>193/MD.98A - 5510/86</t>
+  </si>
+  <si>
+    <t>MUHTASAR VE PRİM HİZMET BEYANNAMESİ GENEL TEBLİĞİ SIRA NO 1'DE DEĞİŞİKLİK YAPILMASINA DAİR TEBLİĞ</t>
+  </si>
+  <si>
+    <t>SOSYAL GÜVENLİK KURUMU BAŞKANLIĞINDA STAJ YAPACAK YÜKSEKÖĞRENİM ÖĞRENCİLERİNİN BELİRLENMESİ VE STAJ SÜRECİNE İLİŞKİN ESASLARIN DÜZENLENMESİ HAKKINDA YÖNERGE</t>
+  </si>
+  <si>
+    <t>SOSYAL GÜVENLİK KURUMU İMZA YETKİLERİ VE YETKİ DEVRİ YÖNERGESİ</t>
+  </si>
+  <si>
+    <t>YATAKLI SAĞLIK TESİSLERİNDE ACİL SERVİS HİZMETLERİNİN UYGULAMA USUL VE ESASLARI HAKKINDA TEBLİĞ</t>
+  </si>
+  <si>
+    <t>3359/MD.3 - 1 NOLU CBK/MD.355, 508</t>
+  </si>
+  <si>
+    <t>YATAKLI TEDAVİ KURUMLARI İŞLETME YÖNETMELİĞİ</t>
+  </si>
+  <si>
+    <t>YATAKLI TEDAVİ KURUMLARI ENFEKSİYON KONTROL YÖNETMELİĞİ</t>
+  </si>
+  <si>
+    <t>3359/MD.3, 9 - 1 NOLU CBK/MD.508</t>
+  </si>
+  <si>
+    <t>ACİL SAĞLIK HİZMETLERİ YÖNETMELİĞİ</t>
+  </si>
+  <si>
+    <t>3359/MD.3, 9 - 1219/MD.3 - 2918/MD.8 - 663 KHK/MD.9, 40</t>
+  </si>
+  <si>
+    <t>BİLİRKİŞİLİK YÖNETMELİĞİ</t>
+  </si>
+  <si>
+    <t>6754/MD.18</t>
+  </si>
+  <si>
+    <t>TURKUAZ KART YÖNETMELİĞİ</t>
+  </si>
+  <si>
+    <t>65 Yaşını Doldurmuş Muhtaç, Güçsüz ve Kimsesiz Türk Vatandaşları ile Engelli ve Muhtaç Türk Vatandaşlarına Aylık Bağlanması Hakkında Yönetmelik</t>
+  </si>
+  <si>
+    <t>2022/MD.4</t>
+  </si>
+  <si>
+    <t>BAKANLIK REHBERİ</t>
+  </si>
+  <si>
+    <t>Meslek Hastalıkları Rehberi</t>
+  </si>
+  <si>
+    <t>Dış Giyim Eşyaları İmali İşyerleri Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>Mobilya İmalatı İşyerleri Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>KARAYOLU İLE YÜK TAŞIMACILIĞI, EV VE İŞYERLERİNE VERİLEN TAŞIMACILIK VE YÜKLEME-BOŞALTMA HİZMETLERİ Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>ENTEGRE ET ÜRETİMİ Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>4483 sayılı Kanun Ön İnceleme Rehberi</t>
+  </si>
+  <si>
+    <t>Bisküvi, Dayanıklı Pastane Ürünleri ve Kek İmalatı İşyerleri Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>DENİZ NAKLİYAT VE ULAŞTIRMASI SEKTÖRÜNDE ASGARİ İŞÇİLİK İNCELEME KILAVUZU</t>
+  </si>
+  <si>
+    <t>Deri Giyim Eşyası İmalatı İşyerleri Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>ÖZEL ÖĞRETİM KURUMLARI Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>Pamuklu Dokuma İmalatı İşyerleri Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>Toplu Yemek İmalatı İşyerleri Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>REHBERLIK VE TEFTİŞ BAŞKANLIĞI TEFTİŞ YÖNETİM SİSTEMİ UYGULAMA USUL VE ESASLARI</t>
+  </si>
+  <si>
+    <t>5502/MD.17</t>
+  </si>
+  <si>
+    <t>2017/1</t>
+  </si>
+  <si>
+    <t>TYS UYGULAMA USUL VE ESASLARI</t>
+  </si>
+  <si>
+    <t>Rapor İstatistik Özeti</t>
+  </si>
+  <si>
+    <t>2009/3</t>
+  </si>
+  <si>
+    <t>Uygulama birliğinin sağlanması ve standart oluşturulması</t>
+  </si>
+  <si>
+    <t>2013/1</t>
+  </si>
+  <si>
+    <t>Çalışma Cetvellerinin Kontrol ve Gönderilme Esasları</t>
+  </si>
+  <si>
+    <t>2009/1</t>
+  </si>
+  <si>
+    <t>Uygulamada Birliktelik</t>
+  </si>
+  <si>
+    <t>2010/4</t>
+  </si>
+  <si>
+    <t>2010/04 sayılı iç emirde değişiklik</t>
+  </si>
+  <si>
+    <t>2010/5</t>
+  </si>
+  <si>
+    <t>2011/2</t>
+  </si>
+  <si>
+    <t>İŞ KAZASI İNCELEMELERİ</t>
+  </si>
+  <si>
+    <t>Asgarî İşçilik İncelemelerinde Süre</t>
+  </si>
+  <si>
+    <t>2011/4</t>
+  </si>
+  <si>
+    <t>Uygulamada birliktelik sağlanması</t>
+  </si>
+  <si>
+    <t>2012/1</t>
+  </si>
+  <si>
+    <t>İş Kazası ve Meslek Hastalığı Soruşturmaları</t>
+  </si>
+  <si>
+    <t>2014/4</t>
+  </si>
+  <si>
+    <t>SÖZLEŞME VE PROTOKOL UYGULAMASI</t>
+  </si>
+  <si>
+    <t>2015/6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uygulama birliğinin sağlanması </t>
+  </si>
+  <si>
+    <t>2015/1</t>
+  </si>
+  <si>
+    <t>MUHTELİF KONULAR</t>
+  </si>
+  <si>
+    <t>2016/3</t>
+  </si>
+  <si>
+    <t>2018/2 SAYILI İÇ EMİR</t>
+  </si>
+  <si>
+    <t>2018/2</t>
+  </si>
+  <si>
+    <t>TASARRUF TEDBİRLERİ GENELGESİ</t>
+  </si>
+  <si>
+    <t>2021/1</t>
+  </si>
+  <si>
+    <t>2025.1</t>
+  </si>
+  <si>
+    <t>KOMİSYONLARIN GÖREVLERİ</t>
+  </si>
+  <si>
+    <t>MEMURİYET MAHALLİ İÇİNDE YOL MASRAFI</t>
+  </si>
+  <si>
+    <t>100 SORUDA E-DEFTER</t>
+  </si>
+  <si>
+    <t>KILAVUZ</t>
+  </si>
+  <si>
+    <t>2022/1</t>
+  </si>
+  <si>
+    <t>RAPOR TESLİMİ</t>
+  </si>
+  <si>
+    <t>RESMİ YAZIŞMA KILAVUZU</t>
+  </si>
+  <si>
+    <t>ASGARİ İŞÇİLİK REHBERİ</t>
+  </si>
+  <si>
+    <t>REHBER</t>
+  </si>
+  <si>
+    <t>TEBLİGAT İŞLETME USUL VE ESASLARI</t>
+  </si>
+  <si>
+    <t>7201 - 213</t>
+  </si>
+  <si>
+    <t>GELİR VERGİSİ GENEL TEBLİĞİ (SERİ NO: 319)</t>
+  </si>
+  <si>
+    <t>193 - 7349</t>
+  </si>
+  <si>
+    <t>AVRUPA BİRLİĞİ'NDE SOSYAL GÜVENLİK</t>
+  </si>
+  <si>
+    <t>SOSYAL GÜVENLİK SÖZLÜĞÜ TR-EN VE EN-TR</t>
+  </si>
+  <si>
+    <t>SAĞLIK RAPORLARINA İLİŞKİN USUL VE ESASLAR</t>
+  </si>
+  <si>
+    <t>GEÇİCİ KORUMA SAĞLANAN YABANCILARIN ÇALIŞMA İZİNLERİNE DAİR YÖNETMELİK</t>
+  </si>
+  <si>
+    <t>6458/MD.91</t>
+  </si>
+  <si>
+    <t>GEÇİCİ KORUMA YÖNETMELİĞİ</t>
+  </si>
+  <si>
+    <t>5604 SAYILI MALİ TATİL İHDAS EDİLMESİ HAKKINDA KANUNUN 2 NCİ MADDESİNİN UYGULANMASINA İLİŞKİN TEBLİĞ</t>
+  </si>
+  <si>
+    <t>5604/MD.2</t>
+  </si>
+  <si>
+    <t>MALÎ TATİL İHDAS EDİLMESİ HAKKINDA KANUN</t>
+  </si>
+  <si>
+    <t>SOSYAL GÜVENLİK KAPSAMINDAKİ SİGORTALILARIN HAK VE YÜKÜMLÜLÜKLERİ</t>
+  </si>
+  <si>
+    <t>ÇALIŞMA VE SOSYAL GÜVENLİK BAKANLIĞI İŞ TEFTİŞ KURULU YÖNETMELİĞİ</t>
+  </si>
+  <si>
+    <t>3146/MD.5, 15</t>
+  </si>
+  <si>
+    <t>RİSK ANALİZİ VE SÜREKLİ DENETİM YÖNERGESİ</t>
+  </si>
+  <si>
+    <t>5502/MD.3 - 5510/MD.59 - RTB YÖNETMELİĞİ/MD.7</t>
+  </si>
+  <si>
+    <t>SOSYAL GÜVENLİK KURUMU GENEL SAĞLIK SİGORTASI VERİLERİNİN GÜVENLİĞİ VE PAYLAŞIMINA İLİŞKİN USUL VE ESASLAR</t>
+  </si>
+  <si>
+    <t>5510/MD.78, 100</t>
+  </si>
+  <si>
+    <t>GENEL SAĞLIK SİGORTASI VERİLERİNİN GÜVENLİĞİ VE PAYLAŞIMINA İLİŞKİN YÖNETMELİK</t>
+  </si>
+  <si>
+    <t>SOSYAL GÜVENLİK KURUMU MİSAFİRHANE VE LOKAL İŞLETME USUL VE ESASLARI</t>
+  </si>
+  <si>
+    <t>TEFTİŞ VE DENETİM REHBERİ</t>
+  </si>
+  <si>
+    <t>Ayakkabı Terlik imalatı Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>Çikolata ve Şekerleme İmalatı İşyerleri Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>DERSHANE Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>ECZANE DENETİM REHBERİ</t>
+  </si>
+  <si>
+    <t>FIRIN İŞLETMELERİ Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>FUTBOL KULÜPLERİ Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>GEÇİCİ KORUMA SAĞLANAN YABANCILARIN ÇALIŞMA İZİNLERİNE DAİR UYGULAMA REHBERİ</t>
+  </si>
+  <si>
+    <t>HASTANE DENETİM REHBERİ</t>
+  </si>
+  <si>
+    <t>İNŞAAT VE İHALELİ İŞLER Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>LOKANTA KAFETERYA SEYYAR YEMEK HİZMETLERİ İŞYERLERİ Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>MESLEK HASTALIKLARI VE İŞLE İLGİLİ HASTALIKLAR TANI REHBERİ</t>
+  </si>
+  <si>
+    <t>MOTORLU TAŞIT VE SÜRÜCÜ KURSLARI Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>OTEL İŞLETMELERİ Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>ÖZEL GÜVENLİK FİRMALARI Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>ÖZEL HASTANE Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>ÖZEL SERVİS ARAÇLARI Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>ÖZEL TEMİZLİK FİRMALARI Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>ŞEHİRİÇİ HALK OTOBÜSLERİ Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>ŞEHİRLERARASI OTOBÜS İŞLETMELERİ Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>TIP MERKEZLERİ Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>ÜNİTE TEFTİŞ REHBERİ</t>
+  </si>
+  <si>
+    <t>YABANCILARIN ÇALIŞMA İZİNLERİ REHBERİ</t>
+  </si>
+  <si>
+    <t>YAPI DENETİM Aİİ REHBERİ</t>
+  </si>
+  <si>
+    <t>Evde doĞum belgesi hakkında</t>
+  </si>
+  <si>
+    <t>Kısa ÇalıŞma ÖdeneĞi Alanlar</t>
+  </si>
+  <si>
+    <t>UNVAN BAZINDA İŞ-GÖREV TANIMLARI KİTABI - 2011</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1919,6 +3223,13 @@
       <charset val="162"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1955,21 +3266,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1978,8 +3289,83 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1987,64 +3373,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2326,7 +3675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E137"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="17"/>
@@ -3056,7 +4405,7 @@
         <v>2972</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>130</v>
@@ -4620,7 +5969,7 @@
         <v>2022</v>
       </c>
       <c r="B135" s="25" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C135" s="16" t="s">
         <v>130</v>
@@ -4637,7 +5986,7 @@
         <v>2893</v>
       </c>
       <c r="B136" s="26" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>130</v>
@@ -4654,7 +6003,7 @@
         <v>5846</v>
       </c>
       <c r="B137" s="31" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>130</v>
@@ -4664,6 +6013,74 @@
       </c>
       <c r="E137" s="30">
         <v>46064</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="17">
+        <v>5083</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="C138" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="D138" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E138" s="34">
+        <v>46072</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="14.4">
+      <c r="A139" s="17">
+        <v>1774</v>
+      </c>
+      <c r="B139" t="s">
+        <v>746</v>
+      </c>
+      <c r="C139" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="D139" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E139" s="34">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="17">
+        <v>3146</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="C140" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="D140" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E140" s="34">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="17">
+        <v>5604</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="C141" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="D141" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E141" s="34">
+        <v>46078</v>
       </c>
     </row>
   </sheetData>
@@ -4677,11 +6094,11 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F406B0C-EF6D-4E36-8ADD-988BCEF63EE0}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.5546875" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.5546875" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.88671875" style="6" bestFit="1" customWidth="1"/>
@@ -4707,16 +6124,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="6" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>547</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>550</v>
       </c>
       <c r="E2" s="7">
         <v>46065</v>
@@ -4724,16 +6141,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="6" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E3" s="7">
         <v>46065</v>
@@ -4741,16 +6158,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>547</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>550</v>
       </c>
       <c r="E4" s="7">
         <v>46065</v>
@@ -4758,19 +6175,308 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="6" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E5" s="7">
         <v>46065</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="6" t="s">
+        <v>923</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>924</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E6" s="7">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="6" t="s">
+        <v>926</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E7" s="7">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="6" t="s">
+        <v>928</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>927</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E8" s="7">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="6" t="s">
+        <v>930</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>929</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E9" s="7">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>931</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E10" s="7">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>933</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E11" s="7">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E12" s="7">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="6" t="s">
+        <v>938</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>937</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E13" s="7">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>939</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E14" s="7">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="6" t="s">
+        <v>942</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>941</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E15" s="7">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="6" t="s">
+        <v>944</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>943</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E16" s="7">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>946</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E17" s="7">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>948</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>947</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E18" s="7">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>950</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>949</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E19" s="7">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>952</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>951</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E20" s="7">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>953</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>954</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E21" s="7">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>958</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>959</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E22" s="7">
+        <v>46077</v>
       </c>
     </row>
   </sheetData>
@@ -4780,13 +6486,13 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC7897AB-3717-4432-BDCC-070EE8BDEEBA}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="57" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1">
@@ -4811,13 +6517,13 @@
         <v>131</v>
       </c>
       <c r="B2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="C2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="E2" s="21">
         <v>46065</v>
@@ -4828,13 +6534,13 @@
         <v>131</v>
       </c>
       <c r="B3" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C3" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D3" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="E3" s="21">
         <v>46065</v>
@@ -4845,10 +6551,10 @@
         <v>131</v>
       </c>
       <c r="B4" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C4" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D4" t="s">
         <v>131</v>
@@ -4862,10 +6568,10 @@
         <v>131</v>
       </c>
       <c r="B5" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C5" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D5" t="s">
         <v>131</v>
@@ -4879,10 +6585,10 @@
         <v>131</v>
       </c>
       <c r="B6" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C6" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D6" t="s">
         <v>131</v>
@@ -4896,10 +6602,10 @@
         <v>131</v>
       </c>
       <c r="B7" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C7" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D7" t="s">
         <v>131</v>
@@ -4913,10 +6619,10 @@
         <v>131</v>
       </c>
       <c r="B8" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="C8" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D8" t="s">
         <v>131</v>
@@ -4930,10 +6636,10 @@
         <v>131</v>
       </c>
       <c r="B9" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C9" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D9" t="s">
         <v>131</v>
@@ -4947,10 +6653,10 @@
         <v>131</v>
       </c>
       <c r="B10" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C10" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D10" t="s">
         <v>131</v>
@@ -4964,10 +6670,10 @@
         <v>131</v>
       </c>
       <c r="B11" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C11" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D11" t="s">
         <v>131</v>
@@ -4981,10 +6687,10 @@
         <v>131</v>
       </c>
       <c r="B12" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C12" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D12" t="s">
         <v>131</v>
@@ -4998,10 +6704,10 @@
         <v>131</v>
       </c>
       <c r="B13" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C13" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D13" t="s">
         <v>131</v>
@@ -5015,10 +6721,10 @@
         <v>131</v>
       </c>
       <c r="B14" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C14" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D14" t="s">
         <v>131</v>
@@ -5032,10 +6738,10 @@
         <v>131</v>
       </c>
       <c r="B15" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C15" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D15" t="s">
         <v>131</v>
@@ -5049,10 +6755,10 @@
         <v>131</v>
       </c>
       <c r="B16" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C16" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D16" t="s">
         <v>131</v>
@@ -5066,16 +6772,710 @@
         <v>131</v>
       </c>
       <c r="B17" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D17" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E17" s="21">
         <v>46065</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B18" t="s">
+        <v>587</v>
+      </c>
+      <c r="C18" t="s">
+        <v>557</v>
+      </c>
+      <c r="E18" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B19" t="s">
+        <v>588</v>
+      </c>
+      <c r="C19" t="s">
+        <v>557</v>
+      </c>
+      <c r="D19" t="s">
+        <v>589</v>
+      </c>
+      <c r="E19" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" t="s">
+        <v>590</v>
+      </c>
+      <c r="C20" t="s">
+        <v>557</v>
+      </c>
+      <c r="D20" t="s">
+        <v>591</v>
+      </c>
+      <c r="E20" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" t="s">
+        <v>592</v>
+      </c>
+      <c r="C21" t="s">
+        <v>557</v>
+      </c>
+      <c r="D21" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" t="s">
+        <v>594</v>
+      </c>
+      <c r="C22" t="s">
+        <v>557</v>
+      </c>
+      <c r="D22" t="s">
+        <v>593</v>
+      </c>
+      <c r="E22" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" t="s">
+        <v>595</v>
+      </c>
+      <c r="C23" t="s">
+        <v>557</v>
+      </c>
+      <c r="D23" t="s">
+        <v>596</v>
+      </c>
+      <c r="E23" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" t="s">
+        <v>597</v>
+      </c>
+      <c r="C24" t="s">
+        <v>557</v>
+      </c>
+      <c r="D24" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>131</v>
+      </c>
+      <c r="B25" t="s">
+        <v>598</v>
+      </c>
+      <c r="C25" t="s">
+        <v>557</v>
+      </c>
+      <c r="D25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E25" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" t="s">
+        <v>599</v>
+      </c>
+      <c r="C26" t="s">
+        <v>557</v>
+      </c>
+      <c r="D26" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>131</v>
+      </c>
+      <c r="B27" t="s">
+        <v>600</v>
+      </c>
+      <c r="C27" t="s">
+        <v>557</v>
+      </c>
+      <c r="D27" t="s">
+        <v>131</v>
+      </c>
+      <c r="E27" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" t="s">
+        <v>601</v>
+      </c>
+      <c r="C28" t="s">
+        <v>557</v>
+      </c>
+      <c r="D28" t="s">
+        <v>131</v>
+      </c>
+      <c r="E28" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>131</v>
+      </c>
+      <c r="B29" t="s">
+        <v>602</v>
+      </c>
+      <c r="C29" t="s">
+        <v>557</v>
+      </c>
+      <c r="D29" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" t="s">
+        <v>603</v>
+      </c>
+      <c r="C30" t="s">
+        <v>557</v>
+      </c>
+      <c r="D30" t="s">
+        <v>131</v>
+      </c>
+      <c r="E30" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>131</v>
+      </c>
+      <c r="B31" t="s">
+        <v>604</v>
+      </c>
+      <c r="C31" t="s">
+        <v>557</v>
+      </c>
+      <c r="D31" t="s">
+        <v>131</v>
+      </c>
+      <c r="E31" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>131</v>
+      </c>
+      <c r="B32" t="s">
+        <v>605</v>
+      </c>
+      <c r="C32" t="s">
+        <v>557</v>
+      </c>
+      <c r="D32" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>131</v>
+      </c>
+      <c r="B33" t="s">
+        <v>606</v>
+      </c>
+      <c r="C33" t="s">
+        <v>557</v>
+      </c>
+      <c r="D33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E33" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34" t="s">
+        <v>607</v>
+      </c>
+      <c r="C34" t="s">
+        <v>557</v>
+      </c>
+      <c r="D34" t="s">
+        <v>131</v>
+      </c>
+      <c r="E34" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B35" t="s">
+        <v>608</v>
+      </c>
+      <c r="C35" t="s">
+        <v>557</v>
+      </c>
+      <c r="D35" t="s">
+        <v>131</v>
+      </c>
+      <c r="E35" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>131</v>
+      </c>
+      <c r="B36" t="s">
+        <v>609</v>
+      </c>
+      <c r="C36" t="s">
+        <v>557</v>
+      </c>
+      <c r="D36" t="s">
+        <v>131</v>
+      </c>
+      <c r="E36" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>131</v>
+      </c>
+      <c r="B37" t="s">
+        <v>610</v>
+      </c>
+      <c r="C37" t="s">
+        <v>557</v>
+      </c>
+      <c r="D37" t="s">
+        <v>131</v>
+      </c>
+      <c r="E37" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>131</v>
+      </c>
+      <c r="B38" t="s">
+        <v>611</v>
+      </c>
+      <c r="C38" t="s">
+        <v>557</v>
+      </c>
+      <c r="D38" t="s">
+        <v>131</v>
+      </c>
+      <c r="E38" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>131</v>
+      </c>
+      <c r="B39" t="s">
+        <v>612</v>
+      </c>
+      <c r="C39" t="s">
+        <v>557</v>
+      </c>
+      <c r="D39" t="s">
+        <v>131</v>
+      </c>
+      <c r="E39" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>131</v>
+      </c>
+      <c r="B40" t="s">
+        <v>613</v>
+      </c>
+      <c r="C40" t="s">
+        <v>557</v>
+      </c>
+      <c r="D40" t="s">
+        <v>131</v>
+      </c>
+      <c r="E40" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>131</v>
+      </c>
+      <c r="B41" t="s">
+        <v>614</v>
+      </c>
+      <c r="C41" t="s">
+        <v>557</v>
+      </c>
+      <c r="D41" t="s">
+        <v>131</v>
+      </c>
+      <c r="E41" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>131</v>
+      </c>
+      <c r="B42" t="s">
+        <v>793</v>
+      </c>
+      <c r="C42" t="s">
+        <v>557</v>
+      </c>
+      <c r="D42" t="s">
+        <v>131</v>
+      </c>
+      <c r="E42" s="21">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>131</v>
+      </c>
+      <c r="B43" t="s">
+        <v>797</v>
+      </c>
+      <c r="C43" t="s">
+        <v>557</v>
+      </c>
+      <c r="D43" t="s">
+        <v>131</v>
+      </c>
+      <c r="E43" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>131</v>
+      </c>
+      <c r="B44" t="s">
+        <v>805</v>
+      </c>
+      <c r="C44" t="s">
+        <v>557</v>
+      </c>
+      <c r="D44" t="s">
+        <v>131</v>
+      </c>
+      <c r="E44" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" t="s">
+        <v>810</v>
+      </c>
+      <c r="C45" t="s">
+        <v>557</v>
+      </c>
+      <c r="D45" t="s">
+        <v>131</v>
+      </c>
+      <c r="E45" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>131</v>
+      </c>
+      <c r="B46" t="s">
+        <v>811</v>
+      </c>
+      <c r="C46" t="s">
+        <v>557</v>
+      </c>
+      <c r="D46" t="s">
+        <v>131</v>
+      </c>
+      <c r="E46" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>131</v>
+      </c>
+      <c r="B47" t="s">
+        <v>812</v>
+      </c>
+      <c r="C47" t="s">
+        <v>557</v>
+      </c>
+      <c r="D47" t="s">
+        <v>131</v>
+      </c>
+      <c r="E47" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>131</v>
+      </c>
+      <c r="B48" t="s">
+        <v>819</v>
+      </c>
+      <c r="C48" t="s">
+        <v>557</v>
+      </c>
+      <c r="D48" t="s">
+        <v>131</v>
+      </c>
+      <c r="E48" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>131</v>
+      </c>
+      <c r="B49" t="s">
+        <v>820</v>
+      </c>
+      <c r="C49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D49" t="s">
+        <v>131</v>
+      </c>
+      <c r="E49" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" t="s">
+        <v>823</v>
+      </c>
+      <c r="C50" t="s">
+        <v>557</v>
+      </c>
+      <c r="D50" t="s">
+        <v>131</v>
+      </c>
+      <c r="E50" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51" t="s">
+        <v>837</v>
+      </c>
+      <c r="C51" t="s">
+        <v>557</v>
+      </c>
+      <c r="D51" t="s">
+        <v>131</v>
+      </c>
+      <c r="E51" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>131</v>
+      </c>
+      <c r="B52" t="s">
+        <v>843</v>
+      </c>
+      <c r="C52" t="s">
+        <v>557</v>
+      </c>
+      <c r="D52" t="s">
+        <v>131</v>
+      </c>
+      <c r="E52" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>131</v>
+      </c>
+      <c r="B53" t="s">
+        <v>844</v>
+      </c>
+      <c r="C53" t="s">
+        <v>557</v>
+      </c>
+      <c r="D53" t="s">
+        <v>131</v>
+      </c>
+      <c r="E53" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>131</v>
+      </c>
+      <c r="B54" t="s">
+        <v>846</v>
+      </c>
+      <c r="C54" t="s">
+        <v>557</v>
+      </c>
+      <c r="D54" t="s">
+        <v>547</v>
+      </c>
+      <c r="E54" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>131</v>
+      </c>
+      <c r="B55" t="s">
+        <v>847</v>
+      </c>
+      <c r="C55" t="s">
+        <v>557</v>
+      </c>
+      <c r="D55" t="s">
+        <v>131</v>
+      </c>
+      <c r="E55" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>131</v>
+      </c>
+      <c r="B56" t="s">
+        <v>853</v>
+      </c>
+      <c r="C56" t="s">
+        <v>557</v>
+      </c>
+      <c r="D56" t="s">
+        <v>131</v>
+      </c>
+      <c r="E56" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>131</v>
+      </c>
+      <c r="B57" t="s">
+        <v>862</v>
+      </c>
+      <c r="C57" t="s">
+        <v>557</v>
+      </c>
+      <c r="D57" t="s">
+        <v>131</v>
+      </c>
+      <c r="E57" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" t="s">
+        <v>955</v>
+      </c>
+      <c r="C58" t="s">
+        <v>557</v>
+      </c>
+      <c r="D58" t="s">
+        <v>131</v>
+      </c>
+      <c r="E58" s="21">
+        <v>46078</v>
       </c>
     </row>
   </sheetData>
@@ -5085,34 +7485,1529 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F8718D7-D631-4F4B-950E-64A96BC13D1A}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="106.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15" thickBot="1">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" t="s">
+        <v>914</v>
+      </c>
+      <c r="C2" t="s">
+        <v>962</v>
+      </c>
+      <c r="D2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E2" s="21">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" t="s">
+        <v>915</v>
+      </c>
+      <c r="C3" t="s">
+        <v>961</v>
+      </c>
+      <c r="D3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E3" s="21">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" t="s">
+        <v>917</v>
+      </c>
+      <c r="C4" t="s">
+        <v>961</v>
+      </c>
+      <c r="D4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E4" s="21">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" t="s">
+        <v>910</v>
+      </c>
+      <c r="C5" t="s">
+        <v>961</v>
+      </c>
+      <c r="D5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E5" s="21">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" t="s">
+        <v>912</v>
+      </c>
+      <c r="C6" t="s">
+        <v>961</v>
+      </c>
+      <c r="D6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" s="21">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" t="s">
+        <v>911</v>
+      </c>
+      <c r="C7" t="s">
+        <v>961</v>
+      </c>
+      <c r="D7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" s="21">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" t="s">
+        <v>918</v>
+      </c>
+      <c r="C8" t="s">
+        <v>961</v>
+      </c>
+      <c r="D8" t="s">
+        <v>131</v>
+      </c>
+      <c r="E8" s="21">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" t="s">
+        <v>919</v>
+      </c>
+      <c r="C9" t="s">
+        <v>961</v>
+      </c>
+      <c r="D9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" s="21">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" t="s">
+        <v>960</v>
+      </c>
+      <c r="C10" t="s">
+        <v>957</v>
+      </c>
+      <c r="D10" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" t="s">
+        <v>985</v>
+      </c>
+      <c r="C11" t="s">
+        <v>962</v>
+      </c>
+      <c r="D11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E11" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" t="s">
+        <v>920</v>
+      </c>
+      <c r="C12" t="s">
+        <v>961</v>
+      </c>
+      <c r="D12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" s="21">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" t="s">
+        <v>986</v>
+      </c>
+      <c r="C13" t="s">
+        <v>961</v>
+      </c>
+      <c r="D13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" t="s">
+        <v>987</v>
+      </c>
+      <c r="C14" t="s">
+        <v>961</v>
+      </c>
+      <c r="D14" t="s">
+        <v>131</v>
+      </c>
+      <c r="E14" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" t="s">
+        <v>916</v>
+      </c>
+      <c r="C15" t="s">
+        <v>961</v>
+      </c>
+      <c r="D15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E15" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="B16" t="s">
+        <v>988</v>
+      </c>
+      <c r="C16" t="s">
+        <v>961</v>
+      </c>
+      <c r="D16" t="s">
+        <v>131</v>
+      </c>
+      <c r="E16" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" t="s">
+        <v>989</v>
+      </c>
+      <c r="C17" t="s">
+        <v>962</v>
+      </c>
+      <c r="D17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E17" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="B18" t="s">
+        <v>913</v>
+      </c>
+      <c r="C18" t="s">
+        <v>961</v>
+      </c>
+      <c r="D18" t="s">
+        <v>131</v>
+      </c>
+      <c r="E18" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" t="s">
+        <v>990</v>
+      </c>
+      <c r="C19" t="s">
+        <v>961</v>
+      </c>
+      <c r="D19" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" t="s">
+        <v>991</v>
+      </c>
+      <c r="C20" t="s">
+        <v>961</v>
+      </c>
+      <c r="D20" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21" t="s">
+        <v>992</v>
+      </c>
+      <c r="C21" t="s">
+        <v>962</v>
+      </c>
+      <c r="D21" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="B22" t="s">
+        <v>993</v>
+      </c>
+      <c r="C22" t="s">
+        <v>962</v>
+      </c>
+      <c r="D22" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="B23" t="s">
+        <v>994</v>
+      </c>
+      <c r="C23" t="s">
+        <v>961</v>
+      </c>
+      <c r="D23" t="s">
+        <v>131</v>
+      </c>
+      <c r="E23" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24" t="s">
+        <v>995</v>
+      </c>
+      <c r="C24" t="s">
+        <v>961</v>
+      </c>
+      <c r="D24" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" t="s">
+        <v>996</v>
+      </c>
+      <c r="C25" t="s">
+        <v>962</v>
+      </c>
+      <c r="D25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E25" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="B26" t="s">
+        <v>997</v>
+      </c>
+      <c r="C26" t="s">
+        <v>961</v>
+      </c>
+      <c r="D26" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" t="s">
+        <v>998</v>
+      </c>
+      <c r="C27" t="s">
+        <v>961</v>
+      </c>
+      <c r="D27" t="s">
+        <v>131</v>
+      </c>
+      <c r="E27" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28" t="s">
+        <v>999</v>
+      </c>
+      <c r="C28" t="s">
+        <v>961</v>
+      </c>
+      <c r="D28" t="s">
+        <v>131</v>
+      </c>
+      <c r="E28" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
+      <c r="B29" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C29" t="s">
+        <v>961</v>
+      </c>
+      <c r="D29" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5">
+      <c r="B30" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C30" t="s">
+        <v>961</v>
+      </c>
+      <c r="D30" t="s">
+        <v>131</v>
+      </c>
+      <c r="E30" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5">
+      <c r="B31" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C31" t="s">
+        <v>961</v>
+      </c>
+      <c r="D31" t="s">
+        <v>131</v>
+      </c>
+      <c r="E31" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="B32" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C32" t="s">
+        <v>961</v>
+      </c>
+      <c r="D32" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5">
+      <c r="B33" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C33" t="s">
+        <v>961</v>
+      </c>
+      <c r="D33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E33" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5">
+      <c r="B34" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C34" t="s">
+        <v>961</v>
+      </c>
+      <c r="D34" t="s">
+        <v>131</v>
+      </c>
+      <c r="E34" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5">
+      <c r="B35" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C35" t="s">
+        <v>962</v>
+      </c>
+      <c r="D35" t="s">
+        <v>131</v>
+      </c>
+      <c r="E35" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5">
+      <c r="B36" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C36" t="s">
+        <v>962</v>
+      </c>
+      <c r="D36" t="s">
+        <v>131</v>
+      </c>
+      <c r="E36" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5">
+      <c r="B37" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C37" t="s">
+        <v>961</v>
+      </c>
+      <c r="D37" t="s">
+        <v>131</v>
+      </c>
+      <c r="E37" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E12">
+    <sortCondition ref="B1:B12"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E3BD811-4D91-4825-A067-2DC31601BB29}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DBA30C4-D2FF-4575-8682-D915F2A6D489}">
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DBA30C4-D2FF-4575-8682-D915F2A6D489}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="113.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15" thickBot="1">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" t="s">
+        <v>615</v>
+      </c>
+      <c r="C2" t="s">
+        <v>616</v>
+      </c>
+      <c r="D2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E2" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" t="s">
+        <v>617</v>
+      </c>
+      <c r="C3" t="s">
+        <v>616</v>
+      </c>
+      <c r="D3" t="s">
+        <v>547</v>
+      </c>
+      <c r="E3" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C4" t="s">
+        <v>616</v>
+      </c>
+      <c r="D4" t="s">
+        <v>670</v>
+      </c>
+      <c r="E4" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" t="s">
+        <v>720</v>
+      </c>
+      <c r="C5" t="s">
+        <v>616</v>
+      </c>
+      <c r="D5" t="s">
+        <v>698</v>
+      </c>
+      <c r="E5" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" t="s">
+        <v>706</v>
+      </c>
+      <c r="C6" t="s">
+        <v>616</v>
+      </c>
+      <c r="D6" t="s">
+        <v>707</v>
+      </c>
+      <c r="E6" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" t="s">
+        <v>708</v>
+      </c>
+      <c r="C7" t="s">
+        <v>616</v>
+      </c>
+      <c r="D7" t="s">
+        <v>709</v>
+      </c>
+      <c r="E7" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C8" t="s">
+        <v>616</v>
+      </c>
+      <c r="D8" t="s">
+        <v>722</v>
+      </c>
+      <c r="E8" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" t="s">
+        <v>748</v>
+      </c>
+      <c r="C9" t="s">
+        <v>616</v>
+      </c>
+      <c r="D9" t="s">
+        <v>749</v>
+      </c>
+      <c r="E9" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" t="s">
+        <v>752</v>
+      </c>
+      <c r="C10" t="s">
+        <v>753</v>
+      </c>
+      <c r="D10" t="s">
+        <v>754</v>
+      </c>
+      <c r="E10" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" t="s">
+        <v>765</v>
+      </c>
+      <c r="C11" t="s">
+        <v>766</v>
+      </c>
+      <c r="D11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E11" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" t="s">
+        <v>788</v>
+      </c>
+      <c r="C12" t="s">
+        <v>794</v>
+      </c>
+      <c r="D12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" s="21">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" t="s">
+        <v>603</v>
+      </c>
+      <c r="C13" t="s">
+        <v>616</v>
+      </c>
+      <c r="D13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" s="21">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" t="s">
+        <v>791</v>
+      </c>
+      <c r="C14" t="s">
+        <v>616</v>
+      </c>
+      <c r="D14" t="s">
+        <v>131</v>
+      </c>
+      <c r="E14" s="21">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" t="s">
+        <v>792</v>
+      </c>
+      <c r="C15" t="s">
+        <v>616</v>
+      </c>
+      <c r="D15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E15" s="21">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" t="s">
+        <v>795</v>
+      </c>
+      <c r="C16" t="s">
+        <v>616</v>
+      </c>
+      <c r="D16" t="s">
+        <v>131</v>
+      </c>
+      <c r="E16" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B17" t="s">
+        <v>796</v>
+      </c>
+      <c r="C17" t="s">
+        <v>616</v>
+      </c>
+      <c r="D17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E17" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B18" t="s">
+        <v>798</v>
+      </c>
+      <c r="C18" t="s">
+        <v>799</v>
+      </c>
+      <c r="D18" t="s">
+        <v>547</v>
+      </c>
+      <c r="E18" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B19" t="s">
+        <v>800</v>
+      </c>
+      <c r="C19" t="s">
+        <v>616</v>
+      </c>
+      <c r="D19" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" t="s">
+        <v>803</v>
+      </c>
+      <c r="C20" t="s">
+        <v>804</v>
+      </c>
+      <c r="D20" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" t="s">
+        <v>813</v>
+      </c>
+      <c r="C21" t="s">
+        <v>616</v>
+      </c>
+      <c r="D21" t="s">
+        <v>547</v>
+      </c>
+      <c r="E21" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" t="s">
+        <v>814</v>
+      </c>
+      <c r="C22" t="s">
+        <v>616</v>
+      </c>
+      <c r="D22" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" t="s">
+        <v>821</v>
+      </c>
+      <c r="C23" t="s">
+        <v>616</v>
+      </c>
+      <c r="D23" t="s">
+        <v>131</v>
+      </c>
+      <c r="E23" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" t="s">
+        <v>822</v>
+      </c>
+      <c r="C24" t="s">
+        <v>616</v>
+      </c>
+      <c r="D24" t="s">
+        <v>149</v>
+      </c>
+      <c r="E24" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>131</v>
+      </c>
+      <c r="B25" t="s">
+        <v>826</v>
+      </c>
+      <c r="C25" t="s">
+        <v>804</v>
+      </c>
+      <c r="D25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E25" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" t="s">
+        <v>827</v>
+      </c>
+      <c r="C26" t="s">
+        <v>616</v>
+      </c>
+      <c r="D26" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>131</v>
+      </c>
+      <c r="B27" t="s">
+        <v>830</v>
+      </c>
+      <c r="C27" t="s">
+        <v>616</v>
+      </c>
+      <c r="D27" t="s">
+        <v>131</v>
+      </c>
+      <c r="E27" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" t="s">
+        <v>831</v>
+      </c>
+      <c r="C28" t="s">
+        <v>616</v>
+      </c>
+      <c r="D28" t="s">
+        <v>131</v>
+      </c>
+      <c r="E28" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>131</v>
+      </c>
+      <c r="B29" t="s">
+        <v>836</v>
+      </c>
+      <c r="C29" t="s">
+        <v>616</v>
+      </c>
+      <c r="D29" t="s">
+        <v>856</v>
+      </c>
+      <c r="E29" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" t="s">
+        <v>839</v>
+      </c>
+      <c r="C30" t="s">
+        <v>616</v>
+      </c>
+      <c r="D30" t="s">
+        <v>131</v>
+      </c>
+      <c r="E30" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>131</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C31" t="s">
+        <v>616</v>
+      </c>
+      <c r="D31" t="s">
+        <v>131</v>
+      </c>
+      <c r="E31" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>131</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C32" t="s">
+        <v>616</v>
+      </c>
+      <c r="D32" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>131</v>
+      </c>
+      <c r="B33" t="s">
+        <v>840</v>
+      </c>
+      <c r="C33" t="s">
+        <v>804</v>
+      </c>
+      <c r="E33" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34" t="s">
+        <v>841</v>
+      </c>
+      <c r="C34" t="s">
+        <v>616</v>
+      </c>
+      <c r="D34" t="s">
+        <v>547</v>
+      </c>
+      <c r="E34" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B35" t="s">
+        <v>842</v>
+      </c>
+      <c r="C35" t="s">
+        <v>616</v>
+      </c>
+      <c r="D35" t="s">
+        <v>131</v>
+      </c>
+      <c r="E35" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>131</v>
+      </c>
+      <c r="B36" t="s">
+        <v>845</v>
+      </c>
+      <c r="C36" t="s">
+        <v>616</v>
+      </c>
+      <c r="D36" t="s">
+        <v>131</v>
+      </c>
+      <c r="E36" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>131</v>
+      </c>
+      <c r="B37" t="s">
+        <v>851</v>
+      </c>
+      <c r="C37" t="s">
+        <v>616</v>
+      </c>
+      <c r="D37" t="s">
+        <v>131</v>
+      </c>
+      <c r="E37" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>131</v>
+      </c>
+      <c r="B38" t="s">
+        <v>852</v>
+      </c>
+      <c r="C38" t="s">
+        <v>804</v>
+      </c>
+      <c r="D38" t="s">
+        <v>131</v>
+      </c>
+      <c r="E38" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>131</v>
+      </c>
+      <c r="B39" t="s">
+        <v>854</v>
+      </c>
+      <c r="C39" t="s">
+        <v>804</v>
+      </c>
+      <c r="D39" t="s">
+        <v>547</v>
+      </c>
+      <c r="E39" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>131</v>
+      </c>
+      <c r="B40" t="s">
+        <v>855</v>
+      </c>
+      <c r="C40" t="s">
+        <v>616</v>
+      </c>
+      <c r="D40" t="s">
+        <v>856</v>
+      </c>
+      <c r="E40" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>131</v>
+      </c>
+      <c r="B41" t="s">
+        <v>861</v>
+      </c>
+      <c r="C41" t="s">
+        <v>616</v>
+      </c>
+      <c r="D41" t="s">
+        <v>131</v>
+      </c>
+      <c r="E41" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>131</v>
+      </c>
+      <c r="B42" t="s">
+        <v>967</v>
+      </c>
+      <c r="C42" t="s">
+        <v>616</v>
+      </c>
+      <c r="D42" t="s">
+        <v>131</v>
+      </c>
+      <c r="E42" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>131</v>
+      </c>
+      <c r="B43" t="s">
+        <v>618</v>
+      </c>
+      <c r="C43" t="s">
+        <v>619</v>
+      </c>
+      <c r="D43">
+        <v>4483</v>
+      </c>
+      <c r="E43" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>131</v>
+      </c>
+      <c r="B44" t="s">
+        <v>620</v>
+      </c>
+      <c r="C44" t="s">
+        <v>619</v>
+      </c>
+      <c r="D44" t="s">
+        <v>131</v>
+      </c>
+      <c r="E44" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" t="s">
+        <v>621</v>
+      </c>
+      <c r="C45" t="s">
+        <v>619</v>
+      </c>
+      <c r="D45" t="s">
+        <v>131</v>
+      </c>
+      <c r="E45" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>131</v>
+      </c>
+      <c r="B46" t="s">
+        <v>622</v>
+      </c>
+      <c r="C46" t="s">
+        <v>619</v>
+      </c>
+      <c r="D46" t="s">
+        <v>131</v>
+      </c>
+      <c r="E46" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>131</v>
+      </c>
+      <c r="B47" t="s">
+        <v>623</v>
+      </c>
+      <c r="C47" t="s">
+        <v>619</v>
+      </c>
+      <c r="D47" t="s">
+        <v>131</v>
+      </c>
+      <c r="E47" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>131</v>
+      </c>
+      <c r="B48" t="s">
+        <v>624</v>
+      </c>
+      <c r="C48" t="s">
+        <v>619</v>
+      </c>
+      <c r="D48" t="s">
+        <v>131</v>
+      </c>
+      <c r="E48" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>131</v>
+      </c>
+      <c r="B49" t="s">
+        <v>848</v>
+      </c>
+      <c r="C49" t="s">
+        <v>619</v>
+      </c>
+      <c r="D49" t="s">
+        <v>849</v>
+      </c>
+      <c r="E49" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" t="s">
+        <v>850</v>
+      </c>
+      <c r="C50" t="s">
+        <v>619</v>
+      </c>
+      <c r="D50" t="s">
+        <v>131</v>
+      </c>
+      <c r="E50" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51" t="s">
+        <v>860</v>
+      </c>
+      <c r="C51" t="s">
+        <v>619</v>
+      </c>
+      <c r="D51" t="s">
+        <v>131</v>
+      </c>
+      <c r="E51" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>131</v>
+      </c>
+      <c r="B52" t="s">
+        <v>909</v>
+      </c>
+      <c r="C52" t="s">
+        <v>908</v>
+      </c>
+      <c r="D52" t="s">
+        <v>131</v>
+      </c>
+      <c r="E52" s="21">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>131</v>
+      </c>
+      <c r="B53" t="s">
+        <v>956</v>
+      </c>
+      <c r="C53" t="s">
+        <v>957</v>
+      </c>
+      <c r="E53" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>131</v>
+      </c>
+      <c r="B54" t="s">
+        <v>968</v>
+      </c>
+      <c r="C54" t="s">
+        <v>766</v>
+      </c>
+      <c r="D54" t="s">
+        <v>131</v>
+      </c>
+      <c r="E54" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>131</v>
+      </c>
+      <c r="B55" s="47" t="s">
+        <v>976</v>
+      </c>
+      <c r="C55" t="s">
+        <v>957</v>
+      </c>
+      <c r="D55" t="s">
+        <v>131</v>
+      </c>
+      <c r="E55" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E42" xr:uid="{6DBA30C4-D2FF-4575-8682-D915F2A6D489}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{457A2F56-4CA2-4F09-9C5A-1AE2448330FD}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7" style="6" bestFit="1" customWidth="1"/>
@@ -5144,7 +9039,7 @@
       <c r="A2" s="6">
         <v>4</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="40" t="s">
         <v>134</v>
       </c>
       <c r="C2" s="6" t="s">
@@ -5155,6 +9050,23 @@
       </c>
       <c r="E2" s="7">
         <v>46063</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="6">
+        <v>3</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>787</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E3" s="7">
+        <v>46075</v>
       </c>
     </row>
   </sheetData>
@@ -5164,11 +9076,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ADC42A9-1F3F-4AFB-B985-F185653225BC}">
-  <dimension ref="A1:E153"/>
+  <dimension ref="A1:E173"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.5546875" style="10" customWidth="1"/>
+    <col min="2" max="2" width="102.44140625" style="10" customWidth="1"/>
     <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="56.44140625" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.5546875" style="9" bestFit="1" customWidth="1"/>
@@ -5367,7 +9279,7 @@
         <v>16287</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>136</v>
@@ -6217,13 +10129,13 @@
         <v>23413</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>254</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>255</v>
       </c>
       <c r="E62" s="12">
         <v>46064</v>
@@ -6234,13 +10146,13 @@
         <v>21517</v>
       </c>
       <c r="B63" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>257</v>
       </c>
       <c r="E63" s="12">
         <v>46064</v>
@@ -6251,13 +10163,13 @@
         <v>19151</v>
       </c>
       <c r="B64" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>258</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>259</v>
       </c>
       <c r="E64" s="12">
         <v>46064</v>
@@ -6268,13 +10180,13 @@
         <v>19088</v>
       </c>
       <c r="B65" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>261</v>
       </c>
       <c r="E65" s="12">
         <v>46064</v>
@@ -6285,13 +10197,13 @@
         <v>12578</v>
       </c>
       <c r="B66" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>263</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>264</v>
       </c>
       <c r="E66" s="12">
         <v>46064</v>
@@ -6302,13 +10214,13 @@
         <v>12460</v>
       </c>
       <c r="B67" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>266</v>
       </c>
       <c r="E67" s="12">
         <v>46064</v>
@@ -6319,13 +10231,13 @@
         <v>18728</v>
       </c>
       <c r="B68" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>268</v>
       </c>
       <c r="E68" s="12">
         <v>46064</v>
@@ -6336,13 +10248,13 @@
         <v>11404</v>
       </c>
       <c r="B69" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>270</v>
       </c>
       <c r="E69" s="12">
         <v>46064</v>
@@ -6353,13 +10265,13 @@
         <v>39291</v>
       </c>
       <c r="B70" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="E70" s="12">
         <v>46064</v>
@@ -6370,13 +10282,13 @@
         <v>20857</v>
       </c>
       <c r="B71" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>274</v>
       </c>
       <c r="E71" s="12">
         <v>46064</v>
@@ -6387,13 +10299,13 @@
         <v>18989</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E72" s="12">
         <v>46064</v>
@@ -6404,13 +10316,13 @@
         <v>18928</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E73" s="12">
         <v>46064</v>
@@ -6421,13 +10333,13 @@
         <v>18858</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E74" s="12">
         <v>46064</v>
@@ -6438,13 +10350,13 @@
         <v>18829</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E75" s="12">
         <v>46064</v>
@@ -6455,13 +10367,13 @@
         <v>18763</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E76" s="12">
         <v>46064</v>
@@ -6472,13 +10384,13 @@
         <v>18759</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E77" s="12">
         <v>46064</v>
@@ -6489,13 +10401,13 @@
         <v>18741</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E78" s="12">
         <v>46064</v>
@@ -6506,13 +10418,13 @@
         <v>18727</v>
       </c>
       <c r="B79" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D79" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>283</v>
       </c>
       <c r="E79" s="12">
         <v>46064</v>
@@ -6523,13 +10435,13 @@
         <v>18709</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E80" s="12">
         <v>46064</v>
@@ -6540,13 +10452,13 @@
         <v>18695</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E81" s="12">
         <v>46064</v>
@@ -6557,13 +10469,13 @@
         <v>18647</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E82" s="12">
         <v>46064</v>
@@ -6574,13 +10486,13 @@
         <v>18628</v>
       </c>
       <c r="B83" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>287</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>288</v>
       </c>
       <c r="E83" s="12">
         <v>46064</v>
@@ -6591,13 +10503,13 @@
         <v>18627</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E84" s="12">
         <v>46064</v>
@@ -6608,13 +10520,13 @@
         <v>18615</v>
       </c>
       <c r="B85" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>290</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>291</v>
       </c>
       <c r="E85" s="12">
         <v>46064</v>
@@ -6625,13 +10537,13 @@
         <v>18592</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E86" s="12">
         <v>46064</v>
@@ -6642,13 +10554,13 @@
         <v>18588</v>
       </c>
       <c r="B87" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E87" s="12">
         <v>46064</v>
@@ -6659,13 +10571,13 @@
         <v>18581</v>
       </c>
       <c r="B88" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D88" s="4" t="s">
         <v>294</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>295</v>
       </c>
       <c r="E88" s="12">
         <v>46064</v>
@@ -6676,13 +10588,13 @@
         <v>18540</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E89" s="12">
         <v>46064</v>
@@ -6693,13 +10605,13 @@
         <v>18493</v>
       </c>
       <c r="B90" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D90" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>298</v>
       </c>
       <c r="E90" s="12">
         <v>46064</v>
@@ -6710,13 +10622,13 @@
         <v>18485</v>
       </c>
       <c r="B91" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>299</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>300</v>
       </c>
       <c r="E91" s="12">
         <v>46064</v>
@@ -6727,16 +10639,16 @@
         <v>18371</v>
       </c>
       <c r="B92" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="C92" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>302</v>
-      </c>
       <c r="E92" s="12">
-        <v>46064</v>
+        <v>46075</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -6744,13 +10656,13 @@
         <v>18335</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E93" s="12">
         <v>46064</v>
@@ -6761,13 +10673,13 @@
         <v>18318</v>
       </c>
       <c r="B94" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D94" s="4" t="s">
         <v>304</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>305</v>
       </c>
       <c r="E94" s="12">
         <v>46064</v>
@@ -6778,13 +10690,13 @@
         <v>17288</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E95" s="12">
         <v>46064</v>
@@ -6795,13 +10707,13 @@
         <v>17253</v>
       </c>
       <c r="B96" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D96" s="4" t="s">
         <v>307</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>308</v>
       </c>
       <c r="E96" s="12">
         <v>46064</v>
@@ -6812,13 +10724,13 @@
         <v>17050</v>
       </c>
       <c r="B97" s="14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E97" s="12">
         <v>46064</v>
@@ -6829,13 +10741,13 @@
         <v>17031</v>
       </c>
       <c r="B98" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D98" s="4" t="s">
         <v>310</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>311</v>
       </c>
       <c r="E98" s="12">
         <v>46064</v>
@@ -6846,13 +10758,13 @@
         <v>16925</v>
       </c>
       <c r="B99" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D99" s="4" t="s">
         <v>312</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>313</v>
       </c>
       <c r="E99" s="12">
         <v>46064</v>
@@ -6863,13 +10775,13 @@
         <v>16924</v>
       </c>
       <c r="B100" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D100" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>315</v>
       </c>
       <c r="E100" s="12">
         <v>46064</v>
@@ -6880,13 +10792,13 @@
         <v>16923</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E101" s="12">
         <v>46064</v>
@@ -6897,13 +10809,13 @@
         <v>39337</v>
       </c>
       <c r="B102" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D102" s="4" t="s">
         <v>317</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D102" s="4" t="s">
-        <v>318</v>
       </c>
       <c r="E102" s="12">
         <v>46064</v>
@@ -6914,13 +10826,13 @@
         <v>23024</v>
       </c>
       <c r="B103" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D103" s="4" t="s">
         <v>319</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>320</v>
       </c>
       <c r="E103" s="12">
         <v>46064</v>
@@ -6931,13 +10843,13 @@
         <v>20628</v>
       </c>
       <c r="B104" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D104" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D104" s="4" t="s">
-        <v>322</v>
       </c>
       <c r="E104" s="12">
         <v>46064</v>
@@ -6948,13 +10860,13 @@
         <v>18562</v>
       </c>
       <c r="B105" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D105" s="4" t="s">
         <v>323</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>324</v>
       </c>
       <c r="E105" s="12">
         <v>46064</v>
@@ -6965,13 +10877,13 @@
         <v>16855</v>
       </c>
       <c r="B106" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D106" s="4" t="s">
         <v>325</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>326</v>
       </c>
       <c r="E106" s="12">
         <v>46064</v>
@@ -6982,13 +10894,13 @@
         <v>13997</v>
       </c>
       <c r="B107" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D107" s="4" t="s">
         <v>327</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D107" s="4" t="s">
-        <v>328</v>
       </c>
       <c r="E107" s="12">
         <v>46064</v>
@@ -6999,13 +10911,13 @@
         <v>12459</v>
       </c>
       <c r="B108" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D108" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D108" s="4" t="s">
-        <v>330</v>
       </c>
       <c r="E108" s="12">
         <v>46064</v>
@@ -7016,13 +10928,13 @@
         <v>6252</v>
       </c>
       <c r="B109" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D109" s="4" t="s">
         <v>331</v>
-      </c>
-      <c r="C109" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D109" s="4" t="s">
-        <v>332</v>
       </c>
       <c r="E109" s="12">
         <v>46064</v>
@@ -7033,13 +10945,13 @@
         <v>6249</v>
       </c>
       <c r="B110" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D110" s="4" t="s">
         <v>333</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D110" s="4" t="s">
-        <v>334</v>
       </c>
       <c r="E110" s="12">
         <v>46064</v>
@@ -7050,13 +10962,13 @@
         <v>5447</v>
       </c>
       <c r="B111" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D111" s="4" t="s">
         <v>335</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>336</v>
       </c>
       <c r="E111" s="12">
         <v>46064</v>
@@ -7067,13 +10979,13 @@
         <v>5449</v>
       </c>
       <c r="B112" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D112" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>338</v>
       </c>
       <c r="E112" s="12">
         <v>46064</v>
@@ -7084,13 +10996,13 @@
         <v>6247</v>
       </c>
       <c r="B113" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D113" s="4" t="s">
         <v>339</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>340</v>
       </c>
       <c r="E113" s="12">
         <v>46064</v>
@@ -7101,13 +11013,13 @@
         <v>6227</v>
       </c>
       <c r="B114" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D114" s="4" t="s">
         <v>341</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>342</v>
       </c>
       <c r="E114" s="12">
         <v>46064</v>
@@ -7118,13 +11030,13 @@
         <v>12605</v>
       </c>
       <c r="B115" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D115" s="4" t="s">
         <v>343</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D115" s="4" t="s">
-        <v>344</v>
       </c>
       <c r="E115" s="12">
         <v>46064</v>
@@ -7135,13 +11047,13 @@
         <v>5454</v>
       </c>
       <c r="B116" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D116" s="4" t="s">
         <v>345</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D116" s="4" t="s">
-        <v>346</v>
       </c>
       <c r="E116" s="12">
         <v>46064</v>
@@ -7152,13 +11064,13 @@
         <v>5463</v>
       </c>
       <c r="B117" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D117" s="4" t="s">
         <v>347</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D117" s="4" t="s">
-        <v>348</v>
       </c>
       <c r="E117" s="12">
         <v>46064</v>
@@ -7169,13 +11081,13 @@
         <v>6251</v>
       </c>
       <c r="B118" s="14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E118" s="12">
         <v>46064</v>
@@ -7186,13 +11098,13 @@
         <v>5457</v>
       </c>
       <c r="B119" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D119" s="4" t="s">
         <v>350</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D119" s="4" t="s">
-        <v>351</v>
       </c>
       <c r="E119" s="12">
         <v>46064</v>
@@ -7203,13 +11115,13 @@
         <v>6248</v>
       </c>
       <c r="B120" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D120" s="4" t="s">
         <v>352</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D120" s="4" t="s">
-        <v>353</v>
       </c>
       <c r="E120" s="12">
         <v>46064</v>
@@ -7220,13 +11132,13 @@
         <v>5451</v>
       </c>
       <c r="B121" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D121" s="4" t="s">
         <v>354</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>355</v>
       </c>
       <c r="E121" s="12">
         <v>46064</v>
@@ -7237,13 +11149,13 @@
         <v>12393</v>
       </c>
       <c r="B122" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D122" s="4" t="s">
         <v>356</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D122" s="4" t="s">
-        <v>357</v>
       </c>
       <c r="E122" s="12">
         <v>46064</v>
@@ -7254,13 +11166,13 @@
         <v>40042</v>
       </c>
       <c r="B123" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D123" s="4" t="s">
         <v>358</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>359</v>
       </c>
       <c r="E123" s="12">
         <v>46064</v>
@@ -7271,13 +11183,13 @@
         <v>31300</v>
       </c>
       <c r="B124" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D124" s="4" t="s">
         <v>360</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>361</v>
       </c>
       <c r="E124" s="12">
         <v>46064</v>
@@ -7288,13 +11200,13 @@
         <v>38393</v>
       </c>
       <c r="B125" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D125" s="4" t="s">
         <v>362</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>363</v>
       </c>
       <c r="E125" s="12">
         <v>46064</v>
@@ -7305,13 +11217,13 @@
         <v>15801</v>
       </c>
       <c r="B126" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D126" s="4" t="s">
         <v>364</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>365</v>
       </c>
       <c r="E126" s="12">
         <v>46064</v>
@@ -7322,13 +11234,13 @@
         <v>13013</v>
       </c>
       <c r="B127" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D127" s="4" t="s">
         <v>366</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>367</v>
       </c>
       <c r="E127" s="12">
         <v>46064</v>
@@ -7339,13 +11251,13 @@
         <v>7190</v>
       </c>
       <c r="B128" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D128" s="4" t="s">
         <v>368</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>369</v>
       </c>
       <c r="E128" s="12">
         <v>46064</v>
@@ -7356,13 +11268,13 @@
         <v>19569</v>
       </c>
       <c r="B129" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D129" s="4" t="s">
         <v>370</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D129" s="4" t="s">
-        <v>371</v>
       </c>
       <c r="E129" s="12">
         <v>46064</v>
@@ -7373,13 +11285,13 @@
         <v>15828</v>
       </c>
       <c r="B130" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D130" s="4" t="s">
         <v>372</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D130" s="4" t="s">
-        <v>373</v>
       </c>
       <c r="E130" s="12">
         <v>46064</v>
@@ -7390,13 +11302,13 @@
         <v>5780</v>
       </c>
       <c r="B131" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D131" s="4" t="s">
         <v>374</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D131" s="4" t="s">
-        <v>375</v>
       </c>
       <c r="E131" s="12">
         <v>46064</v>
@@ -7407,13 +11319,13 @@
         <v>4650</v>
       </c>
       <c r="B132" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D132" s="4" t="s">
         <v>376</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D132" s="4" t="s">
-        <v>377</v>
       </c>
       <c r="E132" s="12">
         <v>46064</v>
@@ -7424,13 +11336,13 @@
         <v>5040</v>
       </c>
       <c r="B133" s="14" t="s">
+        <v>377</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D133" s="4" t="s">
         <v>378</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>379</v>
       </c>
       <c r="E133" s="12">
         <v>46064</v>
@@ -7441,13 +11353,13 @@
         <v>17235</v>
       </c>
       <c r="B134" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D134" s="4" t="s">
         <v>380</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>381</v>
       </c>
       <c r="E134" s="12">
         <v>46064</v>
@@ -7458,13 +11370,13 @@
         <v>40421</v>
       </c>
       <c r="B135" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D135" s="4" t="s">
         <v>382</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D135" s="4" t="s">
-        <v>383</v>
       </c>
       <c r="E135" s="12">
         <v>46064</v>
@@ -7475,13 +11387,13 @@
         <v>39749</v>
       </c>
       <c r="B136" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D136" s="4" t="s">
         <v>384</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D136" s="4" t="s">
-        <v>385</v>
       </c>
       <c r="E136" s="12">
         <v>46064</v>
@@ -7492,13 +11404,13 @@
         <v>4847</v>
       </c>
       <c r="B137" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D137" s="4" t="s">
         <v>386</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D137" s="4" t="s">
-        <v>387</v>
       </c>
       <c r="E137" s="12">
         <v>46064</v>
@@ -7509,13 +11421,13 @@
         <v>85743</v>
       </c>
       <c r="B138" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D138" s="4" t="s">
         <v>388</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D138" s="4" t="s">
-        <v>389</v>
       </c>
       <c r="E138" s="12">
         <v>46064</v>
@@ -7526,7 +11438,7 @@
         <v>85105</v>
       </c>
       <c r="B139" s="14" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>136</v>
@@ -7543,7 +11455,7 @@
         <v>848345</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>136</v>
@@ -7560,7 +11472,7 @@
         <v>8611220</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>136</v>
@@ -7577,7 +11489,7 @@
         <v>836061</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>136</v>
@@ -7594,7 +11506,7 @@
         <v>20023975</v>
       </c>
       <c r="B143" s="14" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>136</v>
@@ -7611,13 +11523,13 @@
         <v>79493</v>
       </c>
       <c r="B144" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D144" s="4" t="s">
         <v>395</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D144" s="4" t="s">
-        <v>396</v>
       </c>
       <c r="E144" s="12">
         <v>46064</v>
@@ -7628,13 +11540,13 @@
         <v>9014</v>
       </c>
       <c r="B145" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D145" s="4" t="s">
         <v>397</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D145" s="4" t="s">
-        <v>398</v>
       </c>
       <c r="E145" s="12">
         <v>46064</v>
@@ -7645,7 +11557,7 @@
         <v>836510</v>
       </c>
       <c r="B146" s="14" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>136</v>
@@ -7662,7 +11574,7 @@
         <v>20112226</v>
       </c>
       <c r="B147" s="14" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>136</v>
@@ -7679,13 +11591,13 @@
         <v>4633</v>
       </c>
       <c r="B148" s="22" t="s">
+        <v>403</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D148" s="23" t="s">
         <v>404</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D148" s="23" t="s">
-        <v>405</v>
       </c>
       <c r="E148" s="24">
         <v>46064</v>
@@ -7696,13 +11608,13 @@
         <v>191</v>
       </c>
       <c r="B149" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D149" s="23" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E149" s="24">
         <v>46064</v>
@@ -7710,16 +11622,16 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="23" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B150" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D150" s="23" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E150" s="24">
         <v>46064</v>
@@ -7730,13 +11642,13 @@
         <v>2646</v>
       </c>
       <c r="B151" s="28" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D151" s="23" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E151" s="24">
         <v>46064</v>
@@ -7747,13 +11659,13 @@
         <v>200610932</v>
       </c>
       <c r="B152" s="28" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D152" s="23" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="E152" s="24">
         <v>46064</v>
@@ -7764,7 +11676,7 @@
         <v>911779</v>
       </c>
       <c r="B153" s="32" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C153" s="33" t="s">
         <v>136</v>
@@ -7776,7 +11688,348 @@
         <v>46067</v>
       </c>
     </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="9">
+        <v>200915169</v>
+      </c>
+      <c r="B154" s="35" t="s">
+        <v>653</v>
+      </c>
+      <c r="C154" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="D154" s="36" t="s">
+        <v>654</v>
+      </c>
+      <c r="E154" s="24">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="9">
+        <v>9484</v>
+      </c>
+      <c r="B155" t="s">
+        <v>747</v>
+      </c>
+      <c r="C155" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="D155" s="9">
+        <v>1774</v>
+      </c>
+      <c r="E155" s="24">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="36">
+        <v>26959</v>
+      </c>
+      <c r="B156" s="10" t="s">
+        <v>760</v>
+      </c>
+      <c r="C156" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="D156" s="36" t="s">
+        <v>761</v>
+      </c>
+      <c r="E156" s="24">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" s="9">
+        <v>85336</v>
+      </c>
+      <c r="B157" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="C157" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="D157" s="36" t="s">
+        <v>764</v>
+      </c>
+      <c r="E157" s="24">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" s="9">
+        <v>31298</v>
+      </c>
+      <c r="B158" s="37" t="s">
+        <v>770</v>
+      </c>
+      <c r="C158" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="D158" s="38" t="s">
+        <v>771</v>
+      </c>
+      <c r="E158" s="24">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" s="9">
+        <v>44939</v>
+      </c>
+      <c r="B159" s="39" t="s">
+        <v>779</v>
+      </c>
+      <c r="C159" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="D159" s="38" t="s">
+        <v>780</v>
+      </c>
+      <c r="E159" s="24">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="B160" t="s">
+        <v>781</v>
+      </c>
+      <c r="C160" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="D160" s="9">
+        <v>4857</v>
+      </c>
+      <c r="E160" s="24">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="B161" s="39" t="s">
+        <v>784</v>
+      </c>
+      <c r="C161" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="D161" s="38" t="s">
+        <v>785</v>
+      </c>
+      <c r="E161" s="24">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" s="9">
+        <v>42369</v>
+      </c>
+      <c r="B162" s="39" t="s">
+        <v>815</v>
+      </c>
+      <c r="C162" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="D162" s="38" t="s">
+        <v>816</v>
+      </c>
+      <c r="E162" s="24">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" s="9">
+        <v>90748</v>
+      </c>
+      <c r="B163" s="41" t="s">
+        <v>832</v>
+      </c>
+      <c r="C163" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="D163" s="9">
+        <v>3628</v>
+      </c>
+      <c r="E163" s="24">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" s="9">
+        <v>20069972</v>
+      </c>
+      <c r="B164" s="41" t="s">
+        <v>858</v>
+      </c>
+      <c r="C164" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="D164" s="42" t="s">
+        <v>859</v>
+      </c>
+      <c r="E164" s="24">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" s="9">
+        <v>85319</v>
+      </c>
+      <c r="B165" s="44" t="s">
+        <v>898</v>
+      </c>
+      <c r="C165" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="D165" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="E165" s="24">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" s="9">
+        <v>42778</v>
+      </c>
+      <c r="B166" s="44" t="s">
+        <v>899</v>
+      </c>
+      <c r="C166" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="D166" s="45" t="s">
+        <v>900</v>
+      </c>
+      <c r="E166" s="24">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" s="9">
+        <v>4798</v>
+      </c>
+      <c r="B167" s="44" t="s">
+        <v>901</v>
+      </c>
+      <c r="C167" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="D167" s="45" t="s">
+        <v>902</v>
+      </c>
+      <c r="E167" s="24">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" s="9">
+        <v>23818</v>
+      </c>
+      <c r="B168" s="44" t="s">
+        <v>903</v>
+      </c>
+      <c r="C168" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="D168" s="45" t="s">
+        <v>904</v>
+      </c>
+      <c r="E168" s="24">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" s="9">
+        <v>17049</v>
+      </c>
+      <c r="B169" s="44" t="s">
+        <v>906</v>
+      </c>
+      <c r="C169" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="D169" s="45" t="s">
+        <v>907</v>
+      </c>
+      <c r="E169" s="46">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" s="9">
+        <v>20168375</v>
+      </c>
+      <c r="B170" s="44" t="s">
+        <v>970</v>
+      </c>
+      <c r="C170" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="D170" s="45" t="s">
+        <v>971</v>
+      </c>
+      <c r="E170" s="24">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="9">
+        <v>20146883</v>
+      </c>
+      <c r="B171" s="44" t="s">
+        <v>972</v>
+      </c>
+      <c r="C171" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="D171" s="45" t="s">
+        <v>971</v>
+      </c>
+      <c r="E171" s="24">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="9">
+        <v>16724</v>
+      </c>
+      <c r="B172" s="44" t="s">
+        <v>977</v>
+      </c>
+      <c r="C172" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="D172" s="45" t="s">
+        <v>978</v>
+      </c>
+      <c r="E172" s="24">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="9">
+        <v>28350</v>
+      </c>
+      <c r="B173" s="44" t="s">
+        <v>983</v>
+      </c>
+      <c r="C173" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="D173" s="45" t="s">
+        <v>982</v>
+      </c>
+      <c r="E173" s="24">
+        <v>46078</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E157" xr:uid="{3ADC42A9-1F3F-4AFB-B985-F185653225BC}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7815,10 +12068,10 @@
         <v>74496</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D2">
         <v>506</v>
@@ -7832,13 +12085,13 @@
         <v>41053</v>
       </c>
       <c r="B3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C3" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D3" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="E3" s="21">
         <v>46064</v>
@@ -7849,10 +12102,10 @@
         <v>131</v>
       </c>
       <c r="B4" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C4" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D4">
         <v>1475</v>
@@ -7866,10 +12119,10 @@
         <v>131</v>
       </c>
       <c r="B5" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C5" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D5">
         <v>2893</v>
@@ -7883,10 +12136,10 @@
         <v>131</v>
       </c>
       <c r="B6" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C6" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D6">
         <v>1475</v>
@@ -7903,10 +12156,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FE7A237-9671-475B-9E8A-4F995EC06DA8}">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7929,64 +12182,64 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>407</v>
+        <v>630</v>
       </c>
       <c r="B2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C2" t="s">
         <v>408</v>
       </c>
-      <c r="C2" t="s">
-        <v>409</v>
-      </c>
       <c r="D2" t="s">
         <v>131</v>
       </c>
       <c r="E2" s="21">
-        <v>46064</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>410</v>
+        <v>632</v>
       </c>
       <c r="B3" t="s">
-        <v>411</v>
+        <v>631</v>
       </c>
       <c r="C3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D3" t="s">
         <v>131</v>
       </c>
       <c r="E3" s="21">
-        <v>46064</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>413</v>
+        <v>629</v>
       </c>
       <c r="B4" t="s">
-        <v>412</v>
+        <v>627</v>
       </c>
       <c r="C4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D4" t="s">
         <v>131</v>
       </c>
       <c r="E4" s="21">
-        <v>46064</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>414</v>
+        <v>484</v>
       </c>
       <c r="B5" t="s">
-        <v>415</v>
+        <v>483</v>
       </c>
       <c r="C5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D5" t="s">
         <v>131</v>
@@ -7997,30 +12250,30 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>416</v>
+        <v>626</v>
       </c>
       <c r="B6" t="s">
-        <v>417</v>
+        <v>625</v>
       </c>
       <c r="C6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D6" t="s">
         <v>131</v>
       </c>
       <c r="E6" s="21">
-        <v>46064</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>418</v>
+        <v>482</v>
       </c>
       <c r="B7" t="s">
-        <v>419</v>
+        <v>481</v>
       </c>
       <c r="C7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D7" t="s">
         <v>131</v>
@@ -8031,115 +12284,115 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>421</v>
+        <v>642</v>
       </c>
       <c r="B8" t="s">
-        <v>420</v>
+        <v>641</v>
       </c>
       <c r="C8" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D8" t="s">
         <v>131</v>
       </c>
       <c r="E8" s="21">
-        <v>46064</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>423</v>
+        <v>636</v>
       </c>
       <c r="B9" t="s">
-        <v>422</v>
+        <v>635</v>
       </c>
       <c r="C9" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D9" t="s">
         <v>131</v>
       </c>
       <c r="E9" s="21">
-        <v>46064</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>424</v>
+        <v>638</v>
       </c>
       <c r="B10" t="s">
-        <v>425</v>
+        <v>637</v>
       </c>
       <c r="C10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D10" t="s">
         <v>131</v>
       </c>
       <c r="E10" s="21">
-        <v>46064</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>426</v>
+        <v>633</v>
       </c>
       <c r="B11" t="s">
-        <v>427</v>
+        <v>634</v>
       </c>
       <c r="C11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D11" t="s">
         <v>131</v>
       </c>
       <c r="E11" s="21">
-        <v>46064</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>428</v>
+        <v>640</v>
       </c>
       <c r="B12" t="s">
-        <v>429</v>
+        <v>639</v>
       </c>
       <c r="C12" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D12" t="s">
         <v>131</v>
       </c>
       <c r="E12" s="21">
-        <v>46064</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>431</v>
+        <v>662</v>
       </c>
       <c r="B13" t="s">
-        <v>430</v>
+        <v>661</v>
       </c>
       <c r="C13" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D13" t="s">
         <v>131</v>
       </c>
       <c r="E13" s="21">
-        <v>46064</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="B14" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C14" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D14" t="s">
         <v>131</v>
@@ -8150,81 +12403,81 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>434</v>
+        <v>644</v>
       </c>
       <c r="B15" t="s">
-        <v>435</v>
+        <v>643</v>
       </c>
       <c r="C15" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D15" t="s">
         <v>131</v>
       </c>
       <c r="E15" s="21">
-        <v>46064</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>436</v>
+        <v>650</v>
       </c>
       <c r="B16" t="s">
-        <v>437</v>
+        <v>649</v>
       </c>
       <c r="C16" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D16" t="s">
         <v>131</v>
       </c>
       <c r="E16" s="21">
-        <v>46064</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>438</v>
+        <v>646</v>
       </c>
       <c r="B17" t="s">
-        <v>439</v>
+        <v>645</v>
       </c>
       <c r="C17" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D17" t="s">
         <v>131</v>
       </c>
       <c r="E17" s="21">
-        <v>46064</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>440</v>
+        <v>652</v>
       </c>
       <c r="B18" t="s">
-        <v>441</v>
+        <v>651</v>
       </c>
       <c r="C18" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D18" t="s">
         <v>131</v>
       </c>
       <c r="E18" s="21">
-        <v>46064</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>443</v>
+        <v>480</v>
       </c>
       <c r="B19" t="s">
-        <v>442</v>
+        <v>479</v>
       </c>
       <c r="C19" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D19" t="s">
         <v>131</v>
@@ -8235,64 +12488,64 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>444</v>
+        <v>656</v>
       </c>
       <c r="B20" t="s">
-        <v>445</v>
+        <v>655</v>
       </c>
       <c r="C20" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D20" t="s">
         <v>131</v>
       </c>
       <c r="E20" s="21">
-        <v>46064</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>446</v>
+        <v>658</v>
       </c>
       <c r="B21" t="s">
-        <v>447</v>
+        <v>657</v>
       </c>
       <c r="C21" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D21" t="s">
         <v>131</v>
       </c>
       <c r="E21" s="21">
-        <v>46064</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>449</v>
+        <v>660</v>
       </c>
       <c r="B22" t="s">
-        <v>448</v>
+        <v>659</v>
       </c>
       <c r="C22" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D22" t="s">
         <v>131</v>
       </c>
       <c r="E22" s="21">
-        <v>46064</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>451</v>
+        <v>423</v>
       </c>
       <c r="B23" t="s">
-        <v>450</v>
+        <v>424</v>
       </c>
       <c r="C23" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D23" t="s">
         <v>131</v>
@@ -8303,13 +12556,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>453</v>
+        <v>477</v>
       </c>
       <c r="B24" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
       <c r="C24" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D24" t="s">
         <v>131</v>
@@ -8320,47 +12573,47 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>455</v>
+        <v>664</v>
       </c>
       <c r="B25" t="s">
-        <v>454</v>
+        <v>663</v>
       </c>
       <c r="C25" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D25" t="s">
         <v>131</v>
       </c>
       <c r="E25" s="21">
-        <v>46064</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>456</v>
+        <v>666</v>
       </c>
       <c r="B26" t="s">
-        <v>457</v>
+        <v>665</v>
       </c>
       <c r="C26" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D26" t="s">
         <v>131</v>
       </c>
       <c r="E26" s="21">
-        <v>46064</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="B27" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="C27" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D27" t="s">
         <v>131</v>
@@ -8371,13 +12624,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="B28" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="C28" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D28" t="s">
         <v>131</v>
@@ -8388,13 +12641,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B29" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C29" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D29" t="s">
         <v>131</v>
@@ -8405,13 +12658,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="B30" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="C30" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D30" t="s">
         <v>131</v>
@@ -8422,13 +12675,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
+        <v>466</v>
+      </c>
+      <c r="B31" t="s">
         <v>467</v>
       </c>
-      <c r="B31" t="s">
-        <v>466</v>
-      </c>
       <c r="C31" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D31" t="s">
         <v>131</v>
@@ -8439,13 +12692,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>468</v>
+        <v>579</v>
       </c>
       <c r="B32" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="C32" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D32" t="s">
         <v>131</v>
@@ -8456,13 +12709,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B33" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="C33" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D33" t="s">
         <v>131</v>
@@ -8473,13 +12726,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>472</v>
+        <v>406</v>
       </c>
       <c r="B34" t="s">
-        <v>473</v>
+        <v>407</v>
       </c>
       <c r="C34" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D34" t="s">
         <v>131</v>
@@ -8490,13 +12743,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="B35" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="C35" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D35" t="s">
         <v>131</v>
@@ -8507,13 +12760,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="B36" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="C36" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D36" t="s">
         <v>131</v>
@@ -8524,30 +12777,30 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>479</v>
+        <v>573</v>
       </c>
       <c r="B37" t="s">
-        <v>478</v>
+        <v>574</v>
       </c>
       <c r="C37" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D37" t="s">
         <v>131</v>
       </c>
       <c r="E37" s="21">
-        <v>46064</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>582</v>
+        <v>667</v>
       </c>
       <c r="B38" t="s">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="C38" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D38" t="s">
         <v>131</v>
@@ -8558,13 +12811,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>482</v>
+        <v>458</v>
       </c>
       <c r="B39" t="s">
-        <v>481</v>
+        <v>457</v>
       </c>
       <c r="C39" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D39" t="s">
         <v>131</v>
@@ -8575,13 +12828,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>484</v>
+        <v>455</v>
       </c>
       <c r="B40" t="s">
-        <v>483</v>
+        <v>456</v>
       </c>
       <c r="C40" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D40" t="s">
         <v>131</v>
@@ -8592,13 +12845,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>486</v>
+        <v>454</v>
       </c>
       <c r="B41" t="s">
-        <v>485</v>
+        <v>453</v>
       </c>
       <c r="C41" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D41" t="s">
         <v>131</v>
@@ -8609,46 +12862,1276 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>576</v>
+        <v>450</v>
       </c>
       <c r="B42" t="s">
-        <v>577</v>
+        <v>449</v>
       </c>
       <c r="C42" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D42" t="s">
         <v>131</v>
       </c>
       <c r="E42" s="21">
-        <v>46065</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>579</v>
+        <v>452</v>
       </c>
       <c r="B43" t="s">
-        <v>578</v>
+        <v>451</v>
       </c>
       <c r="C43" t="s">
+        <v>408</v>
+      </c>
+      <c r="D43" t="s">
+        <v>131</v>
+      </c>
+      <c r="E43" s="21">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>437</v>
+      </c>
+      <c r="B44" t="s">
+        <v>438</v>
+      </c>
+      <c r="C44" t="s">
+        <v>408</v>
+      </c>
+      <c r="D44" t="s">
+        <v>131</v>
+      </c>
+      <c r="E44" s="21">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>445</v>
+      </c>
+      <c r="B45" t="s">
+        <v>446</v>
+      </c>
+      <c r="C45" t="s">
+        <v>408</v>
+      </c>
+      <c r="D45" t="s">
+        <v>131</v>
+      </c>
+      <c r="E45" s="21">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>448</v>
+      </c>
+      <c r="B46" t="s">
+        <v>447</v>
+      </c>
+      <c r="C46" t="s">
+        <v>408</v>
+      </c>
+      <c r="D46" t="s">
+        <v>131</v>
+      </c>
+      <c r="E46" s="21">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>443</v>
+      </c>
+      <c r="B47" t="s">
+        <v>444</v>
+      </c>
+      <c r="C47" t="s">
+        <v>408</v>
+      </c>
+      <c r="D47" t="s">
+        <v>131</v>
+      </c>
+      <c r="E47" s="21">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>439</v>
+      </c>
+      <c r="B48" t="s">
+        <v>440</v>
+      </c>
+      <c r="C48" t="s">
+        <v>408</v>
+      </c>
+      <c r="D48" t="s">
+        <v>131</v>
+      </c>
+      <c r="E48" s="21">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>435</v>
+      </c>
+      <c r="B49" t="s">
+        <v>436</v>
+      </c>
+      <c r="C49" t="s">
+        <v>408</v>
+      </c>
+      <c r="D49" t="s">
+        <v>131</v>
+      </c>
+      <c r="E49" s="21">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>433</v>
+      </c>
+      <c r="B50" t="s">
+        <v>434</v>
+      </c>
+      <c r="C50" t="s">
+        <v>408</v>
+      </c>
+      <c r="D50" t="s">
+        <v>131</v>
+      </c>
+      <c r="E50" s="21">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>431</v>
+      </c>
+      <c r="B51" t="s">
+        <v>432</v>
+      </c>
+      <c r="C51" t="s">
+        <v>408</v>
+      </c>
+      <c r="D51" t="s">
+        <v>131</v>
+      </c>
+      <c r="E51" s="21">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>430</v>
+      </c>
+      <c r="B52" t="s">
+        <v>429</v>
+      </c>
+      <c r="C52" t="s">
+        <v>408</v>
+      </c>
+      <c r="D52" t="s">
+        <v>131</v>
+      </c>
+      <c r="E52" s="21">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>425</v>
+      </c>
+      <c r="B53" t="s">
+        <v>426</v>
+      </c>
+      <c r="C53" t="s">
+        <v>408</v>
+      </c>
+      <c r="D53" t="s">
+        <v>131</v>
+      </c>
+      <c r="E53" s="21">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>576</v>
+      </c>
+      <c r="B54" t="s">
+        <v>575</v>
+      </c>
+      <c r="C54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D54" t="s">
+        <v>131</v>
+      </c>
+      <c r="E54" s="21">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>427</v>
+      </c>
+      <c r="B55" t="s">
+        <v>428</v>
+      </c>
+      <c r="C55" t="s">
+        <v>408</v>
+      </c>
+      <c r="D55" t="s">
+        <v>131</v>
+      </c>
+      <c r="E55" s="21">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>420</v>
+      </c>
+      <c r="B56" t="s">
+        <v>419</v>
+      </c>
+      <c r="C56" t="s">
+        <v>408</v>
+      </c>
+      <c r="D56" t="s">
+        <v>131</v>
+      </c>
+      <c r="E56" s="21">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>415</v>
+      </c>
+      <c r="B57" t="s">
+        <v>416</v>
+      </c>
+      <c r="C57" t="s">
+        <v>408</v>
+      </c>
+      <c r="D57" t="s">
+        <v>131</v>
+      </c>
+      <c r="E57" s="21">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>422</v>
+      </c>
+      <c r="B58" t="s">
+        <v>421</v>
+      </c>
+      <c r="C58" t="s">
+        <v>408</v>
+      </c>
+      <c r="D58" t="s">
+        <v>131</v>
+      </c>
+      <c r="E58" s="21">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>417</v>
+      </c>
+      <c r="B59" t="s">
+        <v>418</v>
+      </c>
+      <c r="C59" t="s">
+        <v>408</v>
+      </c>
+      <c r="D59" t="s">
+        <v>131</v>
+      </c>
+      <c r="E59" s="21">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>413</v>
+      </c>
+      <c r="B60" t="s">
+        <v>414</v>
+      </c>
+      <c r="C60" t="s">
+        <v>408</v>
+      </c>
+      <c r="D60" t="s">
+        <v>131</v>
+      </c>
+      <c r="E60" s="21">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
         <v>409</v>
       </c>
-      <c r="D43" t="s">
-        <v>131</v>
-      </c>
-      <c r="E43" s="21">
-        <v>46065</v>
-      </c>
+      <c r="B61" t="s">
+        <v>410</v>
+      </c>
+      <c r="C61" t="s">
+        <v>408</v>
+      </c>
+      <c r="D61" t="s">
+        <v>131</v>
+      </c>
+      <c r="E61" s="21">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>412</v>
+      </c>
+      <c r="B62" t="s">
+        <v>411</v>
+      </c>
+      <c r="C62" t="s">
+        <v>408</v>
+      </c>
+      <c r="D62" t="s">
+        <v>131</v>
+      </c>
+      <c r="E62" s="21">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>669</v>
+      </c>
+      <c r="B63" t="s">
+        <v>668</v>
+      </c>
+      <c r="C63" t="s">
+        <v>408</v>
+      </c>
+      <c r="D63" t="s">
+        <v>131</v>
+      </c>
+      <c r="E63" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>672</v>
+      </c>
+      <c r="B64" t="s">
+        <v>671</v>
+      </c>
+      <c r="C64" t="s">
+        <v>408</v>
+      </c>
+      <c r="D64" t="s">
+        <v>131</v>
+      </c>
+      <c r="E64" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>674</v>
+      </c>
+      <c r="B65" t="s">
+        <v>673</v>
+      </c>
+      <c r="C65" t="s">
+        <v>408</v>
+      </c>
+      <c r="D65" t="s">
+        <v>131</v>
+      </c>
+      <c r="E65" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>676</v>
+      </c>
+      <c r="B66" t="s">
+        <v>675</v>
+      </c>
+      <c r="C66" t="s">
+        <v>408</v>
+      </c>
+      <c r="D66" t="s">
+        <v>131</v>
+      </c>
+      <c r="E66" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>677</v>
+      </c>
+      <c r="B67" t="s">
+        <v>438</v>
+      </c>
+      <c r="C67" t="s">
+        <v>408</v>
+      </c>
+      <c r="D67" t="s">
+        <v>131</v>
+      </c>
+      <c r="E67" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>679</v>
+      </c>
+      <c r="B68" t="s">
+        <v>678</v>
+      </c>
+      <c r="C68" t="s">
+        <v>408</v>
+      </c>
+      <c r="D68" t="s">
+        <v>131</v>
+      </c>
+      <c r="E68" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>681</v>
+      </c>
+      <c r="B69" t="s">
+        <v>680</v>
+      </c>
+      <c r="C69" t="s">
+        <v>408</v>
+      </c>
+      <c r="D69" t="s">
+        <v>131</v>
+      </c>
+      <c r="E69" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>683</v>
+      </c>
+      <c r="B70" t="s">
+        <v>682</v>
+      </c>
+      <c r="C70" t="s">
+        <v>408</v>
+      </c>
+      <c r="D70" t="s">
+        <v>131</v>
+      </c>
+      <c r="E70" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>688</v>
+      </c>
+      <c r="B71" t="s">
+        <v>689</v>
+      </c>
+      <c r="C71" t="s">
+        <v>408</v>
+      </c>
+      <c r="D71" t="s">
+        <v>131</v>
+      </c>
+      <c r="E71" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>691</v>
+      </c>
+      <c r="B72" t="s">
+        <v>690</v>
+      </c>
+      <c r="C72" t="s">
+        <v>408</v>
+      </c>
+      <c r="D72" t="s">
+        <v>131</v>
+      </c>
+      <c r="E72" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>693</v>
+      </c>
+      <c r="B73" t="s">
+        <v>692</v>
+      </c>
+      <c r="C73" t="s">
+        <v>408</v>
+      </c>
+      <c r="D73" t="s">
+        <v>131</v>
+      </c>
+      <c r="E73" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>694</v>
+      </c>
+      <c r="B74" t="s">
+        <v>695</v>
+      </c>
+      <c r="C74" t="s">
+        <v>408</v>
+      </c>
+      <c r="D74" t="s">
+        <v>131</v>
+      </c>
+      <c r="E74" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>697</v>
+      </c>
+      <c r="B75" t="s">
+        <v>696</v>
+      </c>
+      <c r="C75" t="s">
+        <v>408</v>
+      </c>
+      <c r="D75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E75" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>700</v>
+      </c>
+      <c r="B76" t="s">
+        <v>699</v>
+      </c>
+      <c r="C76" t="s">
+        <v>408</v>
+      </c>
+      <c r="D76" t="s">
+        <v>131</v>
+      </c>
+      <c r="E76" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>701</v>
+      </c>
+      <c r="B77" t="s">
+        <v>459</v>
+      </c>
+      <c r="C77" t="s">
+        <v>408</v>
+      </c>
+      <c r="D77" t="s">
+        <v>131</v>
+      </c>
+      <c r="E77" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>703</v>
+      </c>
+      <c r="B78" t="s">
+        <v>702</v>
+      </c>
+      <c r="C78" t="s">
+        <v>408</v>
+      </c>
+      <c r="D78" t="s">
+        <v>131</v>
+      </c>
+      <c r="E78" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>705</v>
+      </c>
+      <c r="B79" t="s">
+        <v>704</v>
+      </c>
+      <c r="C79" t="s">
+        <v>408</v>
+      </c>
+      <c r="D79" t="s">
+        <v>131</v>
+      </c>
+      <c r="E79" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>711</v>
+      </c>
+      <c r="B80" t="s">
+        <v>710</v>
+      </c>
+      <c r="C80" t="s">
+        <v>408</v>
+      </c>
+      <c r="D80" t="s">
+        <v>712</v>
+      </c>
+      <c r="E80" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>713</v>
+      </c>
+      <c r="B81" t="s">
+        <v>714</v>
+      </c>
+      <c r="C81" t="s">
+        <v>408</v>
+      </c>
+      <c r="D81" t="s">
+        <v>131</v>
+      </c>
+      <c r="E81" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>715</v>
+      </c>
+      <c r="B82" t="s">
+        <v>888</v>
+      </c>
+      <c r="C82" t="s">
+        <v>408</v>
+      </c>
+      <c r="D82" t="s">
+        <v>131</v>
+      </c>
+      <c r="E82" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>716</v>
+      </c>
+      <c r="B83" t="s">
+        <v>717</v>
+      </c>
+      <c r="C83" t="s">
+        <v>408</v>
+      </c>
+      <c r="D83" t="s">
+        <v>131</v>
+      </c>
+      <c r="E83" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>719</v>
+      </c>
+      <c r="B84" t="s">
+        <v>718</v>
+      </c>
+      <c r="C84" t="s">
+        <v>408</v>
+      </c>
+      <c r="D84" t="s">
+        <v>131</v>
+      </c>
+      <c r="E84" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>724</v>
+      </c>
+      <c r="B85" t="s">
+        <v>723</v>
+      </c>
+      <c r="C85" t="s">
+        <v>408</v>
+      </c>
+      <c r="D85" t="s">
+        <v>131</v>
+      </c>
+      <c r="E85" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>726</v>
+      </c>
+      <c r="B86" t="s">
+        <v>725</v>
+      </c>
+      <c r="C86" t="s">
+        <v>408</v>
+      </c>
+      <c r="D86" t="s">
+        <v>131</v>
+      </c>
+      <c r="E86" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>728</v>
+      </c>
+      <c r="B87" t="s">
+        <v>727</v>
+      </c>
+      <c r="C87" t="s">
+        <v>408</v>
+      </c>
+      <c r="D87" t="s">
+        <v>131</v>
+      </c>
+      <c r="E87" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>730</v>
+      </c>
+      <c r="B88" t="s">
+        <v>729</v>
+      </c>
+      <c r="C88" t="s">
+        <v>408</v>
+      </c>
+      <c r="D88" t="s">
+        <v>131</v>
+      </c>
+      <c r="E88" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>732</v>
+      </c>
+      <c r="B89" t="s">
+        <v>731</v>
+      </c>
+      <c r="C89" t="s">
+        <v>408</v>
+      </c>
+      <c r="D89" t="s">
+        <v>131</v>
+      </c>
+      <c r="E89" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>732</v>
+      </c>
+      <c r="B90" t="s">
+        <v>733</v>
+      </c>
+      <c r="C90" t="s">
+        <v>408</v>
+      </c>
+      <c r="D90" t="s">
+        <v>131</v>
+      </c>
+      <c r="E90" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>734</v>
+      </c>
+      <c r="B91" t="s">
+        <v>735</v>
+      </c>
+      <c r="C91" t="s">
+        <v>408</v>
+      </c>
+      <c r="D91" t="s">
+        <v>131</v>
+      </c>
+      <c r="E91" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>737</v>
+      </c>
+      <c r="B92" t="s">
+        <v>736</v>
+      </c>
+      <c r="C92" t="s">
+        <v>408</v>
+      </c>
+      <c r="D92" t="s">
+        <v>131</v>
+      </c>
+      <c r="E92" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>738</v>
+      </c>
+      <c r="B93" t="s">
+        <v>739</v>
+      </c>
+      <c r="C93" t="s">
+        <v>408</v>
+      </c>
+      <c r="D93" t="s">
+        <v>131</v>
+      </c>
+      <c r="E93" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>740</v>
+      </c>
+      <c r="B94" t="s">
+        <v>741</v>
+      </c>
+      <c r="C94" t="s">
+        <v>408</v>
+      </c>
+      <c r="D94" t="s">
+        <v>131</v>
+      </c>
+      <c r="E94" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>743</v>
+      </c>
+      <c r="B95" t="s">
+        <v>742</v>
+      </c>
+      <c r="C95" t="s">
+        <v>408</v>
+      </c>
+      <c r="D95" t="s">
+        <v>131</v>
+      </c>
+      <c r="E95" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
+        <v>745</v>
+      </c>
+      <c r="B96" t="s">
+        <v>744</v>
+      </c>
+      <c r="C96" t="s">
+        <v>408</v>
+      </c>
+      <c r="D96" t="s">
+        <v>131</v>
+      </c>
+      <c r="E96" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
+        <v>751</v>
+      </c>
+      <c r="B97" t="s">
+        <v>750</v>
+      </c>
+      <c r="C97" t="s">
+        <v>408</v>
+      </c>
+      <c r="D97" t="s">
+        <v>131</v>
+      </c>
+      <c r="E97" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" t="s">
+        <v>756</v>
+      </c>
+      <c r="B98" t="s">
+        <v>755</v>
+      </c>
+      <c r="C98" t="s">
+        <v>408</v>
+      </c>
+      <c r="D98" t="s">
+        <v>131</v>
+      </c>
+      <c r="E98" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
+        <v>740</v>
+      </c>
+      <c r="B99" t="s">
+        <v>757</v>
+      </c>
+      <c r="C99" t="s">
+        <v>408</v>
+      </c>
+      <c r="D99" t="s">
+        <v>131</v>
+      </c>
+      <c r="E99" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
+        <v>758</v>
+      </c>
+      <c r="B100" t="s">
+        <v>759</v>
+      </c>
+      <c r="C100" t="s">
+        <v>408</v>
+      </c>
+      <c r="D100" t="s">
+        <v>131</v>
+      </c>
+      <c r="E100" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" t="s">
+        <v>789</v>
+      </c>
+      <c r="B101" t="s">
+        <v>790</v>
+      </c>
+      <c r="C101" t="s">
+        <v>408</v>
+      </c>
+      <c r="D101" t="s">
+        <v>131</v>
+      </c>
+      <c r="E101" s="21">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" t="s">
+        <v>806</v>
+      </c>
+      <c r="B102" t="s">
+        <v>807</v>
+      </c>
+      <c r="C102" t="s">
+        <v>408</v>
+      </c>
+      <c r="D102" t="s">
+        <v>131</v>
+      </c>
+      <c r="E102" s="21">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" t="s">
+        <v>864</v>
+      </c>
+      <c r="B103" t="s">
+        <v>863</v>
+      </c>
+      <c r="C103" t="s">
+        <v>408</v>
+      </c>
+      <c r="D103" t="s">
+        <v>131</v>
+      </c>
+      <c r="E103" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" t="s">
+        <v>866</v>
+      </c>
+      <c r="B104" t="s">
+        <v>865</v>
+      </c>
+      <c r="C104" t="s">
+        <v>408</v>
+      </c>
+      <c r="D104" t="s">
+        <v>131</v>
+      </c>
+      <c r="E104" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" t="s">
+        <v>868</v>
+      </c>
+      <c r="B105" t="s">
+        <v>867</v>
+      </c>
+      <c r="C105" t="s">
+        <v>408</v>
+      </c>
+      <c r="D105" t="s">
+        <v>131</v>
+      </c>
+      <c r="E105" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" t="s">
+        <v>870</v>
+      </c>
+      <c r="B106" t="s">
+        <v>869</v>
+      </c>
+      <c r="C106" t="s">
+        <v>408</v>
+      </c>
+      <c r="D106" t="s">
+        <v>131</v>
+      </c>
+      <c r="E106" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" t="s">
+        <v>872</v>
+      </c>
+      <c r="B107" t="s">
+        <v>871</v>
+      </c>
+      <c r="C107" t="s">
+        <v>408</v>
+      </c>
+      <c r="D107" t="s">
+        <v>131</v>
+      </c>
+      <c r="E107" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" t="s">
+        <v>874</v>
+      </c>
+      <c r="B108" t="s">
+        <v>873</v>
+      </c>
+      <c r="C108" t="s">
+        <v>408</v>
+      </c>
+      <c r="D108" t="s">
+        <v>131</v>
+      </c>
+      <c r="E108" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" t="s">
+        <v>876</v>
+      </c>
+      <c r="B109" t="s">
+        <v>875</v>
+      </c>
+      <c r="C109" t="s">
+        <v>408</v>
+      </c>
+      <c r="D109" t="s">
+        <v>131</v>
+      </c>
+      <c r="E109" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" t="s">
+        <v>878</v>
+      </c>
+      <c r="B110" t="s">
+        <v>877</v>
+      </c>
+      <c r="C110" t="s">
+        <v>408</v>
+      </c>
+      <c r="D110" t="s">
+        <v>131</v>
+      </c>
+      <c r="E110" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" t="s">
+        <v>879</v>
+      </c>
+      <c r="B111" t="s">
+        <v>880</v>
+      </c>
+      <c r="C111" t="s">
+        <v>408</v>
+      </c>
+      <c r="D111" t="s">
+        <v>131</v>
+      </c>
+      <c r="E111" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" t="s">
+        <v>882</v>
+      </c>
+      <c r="B112" t="s">
+        <v>881</v>
+      </c>
+      <c r="C112" t="s">
+        <v>408</v>
+      </c>
+      <c r="D112" t="s">
+        <v>131</v>
+      </c>
+      <c r="E112" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" t="s">
+        <v>883</v>
+      </c>
+      <c r="B113" t="s">
+        <v>884</v>
+      </c>
+      <c r="C113" t="s">
+        <v>408</v>
+      </c>
+      <c r="D113" t="s">
+        <v>131</v>
+      </c>
+      <c r="E113" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" t="s">
+        <v>885</v>
+      </c>
+      <c r="B114" t="s">
+        <v>886</v>
+      </c>
+      <c r="C114" t="s">
+        <v>408</v>
+      </c>
+      <c r="D114" t="s">
+        <v>131</v>
+      </c>
+      <c r="E114" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" t="s">
+        <v>887</v>
+      </c>
+      <c r="B115" t="s">
+        <v>744</v>
+      </c>
+      <c r="C115" t="s">
+        <v>408</v>
+      </c>
+      <c r="D115" t="s">
+        <v>131</v>
+      </c>
+      <c r="E115" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="E116" s="21"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E62">
+    <sortCondition ref="A1:A62"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDB94204-784F-4A28-80D9-204240483269}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
@@ -8680,10 +14163,10 @@
         <v>198</v>
       </c>
       <c r="B2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C2" t="s">
-        <v>488</v>
+        <v>802</v>
       </c>
       <c r="D2" t="s">
         <v>131</v>
@@ -8694,13 +14177,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B3" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C3" t="s">
-        <v>488</v>
+        <v>802</v>
       </c>
       <c r="D3" t="s">
         <v>131</v>
@@ -8711,13 +14194,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B4" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C4" t="s">
-        <v>488</v>
+        <v>802</v>
       </c>
       <c r="D4" t="s">
         <v>131</v>
@@ -8728,13 +14211,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B5" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C5" t="s">
-        <v>488</v>
+        <v>802</v>
       </c>
       <c r="D5" t="s">
         <v>131</v>
@@ -8748,10 +14231,10 @@
         <v>131</v>
       </c>
       <c r="B6" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C6" t="s">
-        <v>488</v>
+        <v>802</v>
       </c>
       <c r="D6" t="s">
         <v>131</v>
@@ -8765,10 +14248,10 @@
         <v>131</v>
       </c>
       <c r="B7" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C7" t="s">
-        <v>488</v>
+        <v>802</v>
       </c>
       <c r="D7" t="s">
         <v>131</v>
@@ -8782,10 +14265,10 @@
         <v>131</v>
       </c>
       <c r="B8" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C8" t="s">
-        <v>488</v>
+        <v>802</v>
       </c>
       <c r="D8" t="s">
         <v>131</v>
@@ -8796,13 +14279,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B9" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C9" t="s">
-        <v>488</v>
+        <v>802</v>
       </c>
       <c r="D9" t="s">
         <v>131</v>
@@ -8816,10 +14299,10 @@
         <v>131</v>
       </c>
       <c r="B10" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C10" t="s">
-        <v>488</v>
+        <v>802</v>
       </c>
       <c r="D10" t="s">
         <v>131</v>
@@ -8833,10 +14316,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C11" t="s">
-        <v>488</v>
+        <v>802</v>
       </c>
       <c r="D11" t="s">
         <v>131</v>
@@ -8850,16 +14333,271 @@
         <v>131</v>
       </c>
       <c r="B12" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C12" t="s">
-        <v>488</v>
+        <v>802</v>
       </c>
       <c r="D12" t="s">
         <v>131</v>
       </c>
       <c r="E12" s="21">
         <v>46064</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" t="s">
+        <v>647</v>
+      </c>
+      <c r="C13" t="s">
+        <v>802</v>
+      </c>
+      <c r="D13" t="s">
+        <v>648</v>
+      </c>
+      <c r="E13" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" t="s">
+        <v>762</v>
+      </c>
+      <c r="C14" t="s">
+        <v>802</v>
+      </c>
+      <c r="D14">
+        <v>657</v>
+      </c>
+      <c r="E14" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" t="s">
+        <v>801</v>
+      </c>
+      <c r="C15" t="s">
+        <v>802</v>
+      </c>
+      <c r="D15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E15" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" t="s">
+        <v>808</v>
+      </c>
+      <c r="C16" t="s">
+        <v>802</v>
+      </c>
+      <c r="D16" t="s">
+        <v>809</v>
+      </c>
+      <c r="E16" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B17" t="s">
+        <v>824</v>
+      </c>
+      <c r="C17" t="s">
+        <v>802</v>
+      </c>
+      <c r="D17" t="s">
+        <v>825</v>
+      </c>
+      <c r="E17" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B18" t="s">
+        <v>828</v>
+      </c>
+      <c r="C18" t="s">
+        <v>802</v>
+      </c>
+      <c r="D18" t="s">
+        <v>829</v>
+      </c>
+      <c r="E18" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B19" t="s">
+        <v>834</v>
+      </c>
+      <c r="C19" t="s">
+        <v>802</v>
+      </c>
+      <c r="D19" t="s">
+        <v>835</v>
+      </c>
+      <c r="E19" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" t="s">
+        <v>838</v>
+      </c>
+      <c r="C20" t="s">
+        <v>802</v>
+      </c>
+      <c r="D20" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" t="s">
+        <v>857</v>
+      </c>
+      <c r="C21" t="s">
+        <v>802</v>
+      </c>
+      <c r="D21" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" t="s">
+        <v>889</v>
+      </c>
+      <c r="C22" t="s">
+        <v>802</v>
+      </c>
+      <c r="D22" t="s">
+        <v>890</v>
+      </c>
+      <c r="E22" s="21">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" t="s">
+        <v>921</v>
+      </c>
+      <c r="C23" t="s">
+        <v>802</v>
+      </c>
+      <c r="D23" t="s">
+        <v>922</v>
+      </c>
+      <c r="E23" s="21">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" t="s">
+        <v>963</v>
+      </c>
+      <c r="C24" t="s">
+        <v>802</v>
+      </c>
+      <c r="D24" t="s">
+        <v>964</v>
+      </c>
+      <c r="E24" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>131</v>
+      </c>
+      <c r="B25" t="s">
+        <v>969</v>
+      </c>
+      <c r="C25" t="s">
+        <v>802</v>
+      </c>
+      <c r="D25" t="s">
+        <v>818</v>
+      </c>
+      <c r="E25" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" t="s">
+        <v>981</v>
+      </c>
+      <c r="C26" t="s">
+        <v>802</v>
+      </c>
+      <c r="D26" t="s">
+        <v>982</v>
+      </c>
+      <c r="E26" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>131</v>
+      </c>
+      <c r="B27" t="s">
+        <v>984</v>
+      </c>
+      <c r="C27" t="s">
+        <v>802</v>
+      </c>
+      <c r="D27" t="s">
+        <v>131</v>
+      </c>
+      <c r="E27" s="21">
+        <v>46078</v>
       </c>
     </row>
   </sheetData>
@@ -8869,10 +14607,11 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDDE4991-CCDF-41DF-966F-082015B14CDC}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="48.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.88671875" bestFit="1" customWidth="1"/>
   </cols>
@@ -8899,13 +14638,13 @@
         <v>131</v>
       </c>
       <c r="B2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E2" s="21">
         <v>46064</v>
@@ -8916,13 +14655,13 @@
         <v>131</v>
       </c>
       <c r="B3" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C3" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D3" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E3" s="21">
         <v>46064</v>
@@ -8933,13 +14672,13 @@
         <v>131</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C4" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D4" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E4" s="21">
         <v>46064</v>
@@ -8950,10 +14689,13 @@
         <v>131</v>
       </c>
       <c r="B5" t="s">
-        <v>513</v>
+        <v>510</v>
+      </c>
+      <c r="C5" t="s">
+        <v>505</v>
       </c>
       <c r="D5" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E5" s="21">
         <v>46064</v>
@@ -8964,10 +14706,13 @@
         <v>131</v>
       </c>
       <c r="B6" t="s">
-        <v>515</v>
+        <v>512</v>
+      </c>
+      <c r="C6" t="s">
+        <v>505</v>
       </c>
       <c r="D6" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E6" s="21">
         <v>46064</v>
@@ -8978,7 +14723,13 @@
         <v>131</v>
       </c>
       <c r="B7" t="s">
-        <v>580</v>
+        <v>577</v>
+      </c>
+      <c r="C7" t="s">
+        <v>505</v>
+      </c>
+      <c r="D7" t="s">
+        <v>131</v>
       </c>
       <c r="E7" s="21">
         <v>46064</v>
@@ -8989,10 +14740,13 @@
         <v>43929</v>
       </c>
       <c r="B8" t="s">
-        <v>584</v>
+        <v>581</v>
+      </c>
+      <c r="C8" t="s">
+        <v>505</v>
       </c>
       <c r="D8" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="E8" s="21">
         <v>46067</v>
@@ -9003,13 +14757,322 @@
         <v>16909</v>
       </c>
       <c r="B9" t="s">
-        <v>587</v>
+        <v>584</v>
+      </c>
+      <c r="C9" t="s">
+        <v>505</v>
       </c>
       <c r="D9" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E9" s="21">
         <v>46070</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>21500</v>
+      </c>
+      <c r="B10" t="s">
+        <v>684</v>
+      </c>
+      <c r="C10" t="s">
+        <v>505</v>
+      </c>
+      <c r="D10">
+        <v>657</v>
+      </c>
+      <c r="E10" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>18396</v>
+      </c>
+      <c r="B11" t="s">
+        <v>685</v>
+      </c>
+      <c r="C11" t="s">
+        <v>505</v>
+      </c>
+      <c r="D11">
+        <v>657</v>
+      </c>
+      <c r="E11" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>17032</v>
+      </c>
+      <c r="B12" t="s">
+        <v>686</v>
+      </c>
+      <c r="C12" t="s">
+        <v>505</v>
+      </c>
+      <c r="D12">
+        <v>657</v>
+      </c>
+      <c r="E12" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>14913</v>
+      </c>
+      <c r="B13" t="s">
+        <v>687</v>
+      </c>
+      <c r="C13" t="s">
+        <v>505</v>
+      </c>
+      <c r="D13">
+        <v>657</v>
+      </c>
+      <c r="E13" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>18536</v>
+      </c>
+      <c r="B14" t="s">
+        <v>768</v>
+      </c>
+      <c r="C14" t="s">
+        <v>505</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>769</v>
+      </c>
+      <c r="E14" s="21">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>31473</v>
+      </c>
+      <c r="B15" t="s">
+        <v>772</v>
+      </c>
+      <c r="C15" t="s">
+        <v>505</v>
+      </c>
+      <c r="D15">
+        <v>6331</v>
+      </c>
+      <c r="E15" s="21">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>34773</v>
+      </c>
+      <c r="B16" t="s">
+        <v>773</v>
+      </c>
+      <c r="C16" t="s">
+        <v>505</v>
+      </c>
+      <c r="D16">
+        <v>6331</v>
+      </c>
+      <c r="E16" s="21">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>34657</v>
+      </c>
+      <c r="B17" t="s">
+        <v>774</v>
+      </c>
+      <c r="C17" t="s">
+        <v>505</v>
+      </c>
+      <c r="D17">
+        <v>6331</v>
+      </c>
+      <c r="E17" s="21">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>31436</v>
+      </c>
+      <c r="B18" t="s">
+        <v>775</v>
+      </c>
+      <c r="C18" t="s">
+        <v>505</v>
+      </c>
+      <c r="D18">
+        <v>6331</v>
+      </c>
+      <c r="E18" s="21">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>18782</v>
+      </c>
+      <c r="B19" t="s">
+        <v>776</v>
+      </c>
+      <c r="C19" t="s">
+        <v>505</v>
+      </c>
+      <c r="D19" t="s">
+        <v>777</v>
+      </c>
+      <c r="E19" s="21">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>5967</v>
+      </c>
+      <c r="B20" t="s">
+        <v>782</v>
+      </c>
+      <c r="C20" t="s">
+        <v>505</v>
+      </c>
+      <c r="D20" t="s">
+        <v>783</v>
+      </c>
+      <c r="E20" s="21">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>6000</v>
+      </c>
+      <c r="B21" t="s">
+        <v>786</v>
+      </c>
+      <c r="C21" t="s">
+        <v>505</v>
+      </c>
+      <c r="D21">
+        <v>4703</v>
+      </c>
+      <c r="E21" s="21">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>13715</v>
+      </c>
+      <c r="B22" t="s">
+        <v>833</v>
+      </c>
+      <c r="C22" t="s">
+        <v>505</v>
+      </c>
+      <c r="D22">
+        <v>3628</v>
+      </c>
+      <c r="E22" s="21">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" s="43" t="s">
+        <v>891</v>
+      </c>
+      <c r="C23" t="s">
+        <v>505</v>
+      </c>
+      <c r="D23" t="s">
+        <v>892</v>
+      </c>
+      <c r="E23" s="21">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" t="s">
+        <v>893</v>
+      </c>
+      <c r="C24" t="s">
+        <v>505</v>
+      </c>
+      <c r="D24" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" s="21">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>39719</v>
+      </c>
+      <c r="B25" t="s">
+        <v>896</v>
+      </c>
+      <c r="C25" t="s">
+        <v>505</v>
+      </c>
+      <c r="D25" t="s">
+        <v>897</v>
+      </c>
+      <c r="E25" s="21">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" t="s">
+        <v>965</v>
+      </c>
+      <c r="C26" t="s">
+        <v>505</v>
+      </c>
+      <c r="D26" t="s">
+        <v>966</v>
+      </c>
+      <c r="E26" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>11412</v>
+      </c>
+      <c r="B27" t="s">
+        <v>973</v>
+      </c>
+      <c r="C27" t="s">
+        <v>505</v>
+      </c>
+      <c r="D27" t="s">
+        <v>974</v>
+      </c>
+      <c r="E27" s="21">
+        <v>46078</v>
       </c>
     </row>
   </sheetData>
@@ -9019,7 +15082,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D424177-024B-4B2C-8A3E-E442A0E0899C}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
@@ -9051,13 +15114,13 @@
         <v>131</v>
       </c>
       <c r="B2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E2" s="21">
         <v>46064</v>
@@ -9068,13 +15131,13 @@
         <v>131</v>
       </c>
       <c r="B3" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D3" t="s">
         <v>518</v>
-      </c>
-      <c r="D3" t="s">
-        <v>521</v>
       </c>
       <c r="E3" s="21">
         <v>46064</v>
@@ -9085,13 +15148,13 @@
         <v>131</v>
       </c>
       <c r="B4" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C4" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D4" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E4" s="21">
         <v>46064</v>
@@ -9102,13 +15165,13 @@
         <v>131</v>
       </c>
       <c r="B5" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C5" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D5" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E5" s="21">
         <v>46064</v>
@@ -9119,13 +15182,13 @@
         <v>131</v>
       </c>
       <c r="B6" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C6" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D6" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E6" s="21">
         <v>46064</v>
@@ -9136,13 +15199,13 @@
         <v>131</v>
       </c>
       <c r="B7" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C7" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D7" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E7" s="21">
         <v>46064</v>
@@ -9153,13 +15216,13 @@
         <v>131</v>
       </c>
       <c r="B8" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C8" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D8" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="E8" s="21">
         <v>46064</v>
@@ -9170,13 +15233,13 @@
         <v>131</v>
       </c>
       <c r="B9" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C9" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D9" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E9" s="21">
         <v>46064</v>
@@ -9187,13 +15250,13 @@
         <v>131</v>
       </c>
       <c r="B10" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C10" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D10" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="E10" s="21">
         <v>46064</v>
@@ -9204,16 +15267,84 @@
         <v>131</v>
       </c>
       <c r="B11" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C11" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D11" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E11" s="21">
         <v>46064</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" t="s">
+        <v>895</v>
+      </c>
+      <c r="C12" t="s">
+        <v>515</v>
+      </c>
+      <c r="D12" t="s">
+        <v>767</v>
+      </c>
+      <c r="E12" s="21">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" t="s">
+        <v>894</v>
+      </c>
+      <c r="C13" t="s">
+        <v>515</v>
+      </c>
+      <c r="D13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" t="s">
+        <v>979</v>
+      </c>
+      <c r="C14" t="s">
+        <v>515</v>
+      </c>
+      <c r="D14" t="s">
+        <v>980</v>
+      </c>
+      <c r="E14" s="21">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" t="s">
+        <v>817</v>
+      </c>
+      <c r="C15" t="s">
+        <v>515</v>
+      </c>
+      <c r="D15" t="s">
+        <v>818</v>
+      </c>
+      <c r="E15" s="21">
+        <v>46076</v>
       </c>
     </row>
   </sheetData>
